--- a/ROSA_vitaSPEC/Results/test_pretraitements/total.trans.carotenes.natif/Resultats_total.trans.carotenes.natif_moy_diff.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/total.trans.carotenes.natif/Resultats_total.trans.carotenes.natif_moy_diff.xlsx
@@ -211,7 +211,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -223,13 +223,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -255,20 +248,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -291,31 +280,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -619,14 +588,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R47"/>
+  <dimension ref="A1:P47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="16" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="16" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -676,755 +645,754 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
       <c r="B2">
-        <v>3.9900705972905182E-2</v>
+        <v>3.8915285292921757E-2</v>
       </c>
       <c r="C2">
-        <v>6.7889289126977892E-2</v>
+        <v>6.7013611274047813E-2</v>
       </c>
       <c r="D2">
-        <v>9.3456001075664097E-2</v>
+        <v>9.0767685146846855E-2</v>
       </c>
       <c r="E2">
-        <v>8.907204185374662E-2</v>
+        <v>8.5596280374460432E-2</v>
       </c>
       <c r="F2">
-        <v>0.13212070571243281</v>
+        <v>0.1319659088989544</v>
       </c>
       <c r="G2">
-        <v>0.12868567227816191</v>
+        <v>0.1276891677471019</v>
       </c>
       <c r="H2">
-        <v>0.1321624934247824</v>
+        <v>0.12952066162752679</v>
       </c>
       <c r="I2">
-        <v>0.14919183160228841</v>
+        <v>0.14466490960115461</v>
       </c>
       <c r="J2">
-        <v>0.1873460086901895</v>
+        <v>0.18701711596600751</v>
       </c>
       <c r="K2">
-        <v>0.2372719144020288</v>
+        <v>0.2353128907291476</v>
       </c>
       <c r="L2">
-        <v>0.24272949019422529</v>
+        <v>0.24116982832047729</v>
       </c>
       <c r="M2">
-        <v>0.29713860108648471</v>
+        <v>0.30002229171739708</v>
       </c>
       <c r="N2">
-        <v>0.35298109799362082</v>
+        <v>0.35212148822887629</v>
       </c>
       <c r="O2">
-        <v>0.38480908011615589</v>
+        <v>0.37937042812957988</v>
       </c>
       <c r="P2">
-        <v>0.37803043999558078</v>
-      </c>
-      <c r="R2" s="2"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+        <v>0.37722402340742422</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
       <c r="B3">
-        <v>4.3943876475347421E-2</v>
+        <v>4.1947943674877357E-2</v>
       </c>
       <c r="C3">
-        <v>4.1936840755741112E-2</v>
+        <v>4.0141782472616017E-2</v>
       </c>
       <c r="D3">
-        <v>7.9752809078100784E-2</v>
+        <v>7.6349113095919519E-2</v>
       </c>
       <c r="E3">
-        <v>0.1010472504228179</v>
+        <v>0.1071599275775539</v>
       </c>
       <c r="F3">
-        <v>0.1618700175790255</v>
+        <v>0.16463767525544151</v>
       </c>
       <c r="G3">
-        <v>0.19773168368191529</v>
+        <v>0.20332063049081719</v>
       </c>
       <c r="H3">
-        <v>0.28125673160044762</v>
+        <v>0.28870730880481588</v>
       </c>
       <c r="I3">
-        <v>0.31742221592120512</v>
+        <v>0.32641898378987072</v>
       </c>
       <c r="J3">
-        <v>0.35265972908492649</v>
+        <v>0.36235177950524428</v>
       </c>
       <c r="K3">
-        <v>0.35862407774534238</v>
+        <v>0.37103711628550329</v>
       </c>
       <c r="L3">
-        <v>0.39695010147074078</v>
+        <v>0.41055975959907642</v>
       </c>
       <c r="M3">
-        <v>0.47934271535108353</v>
+        <v>0.49354193039229072</v>
       </c>
       <c r="N3">
-        <v>0.55953225006576757</v>
+        <v>0.58036622171148111</v>
       </c>
       <c r="O3">
-        <v>0.62925783297847038</v>
+        <v>0.65080072725065563</v>
       </c>
       <c r="P3">
-        <v>0.6970872561259045</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+        <v>0.72041323687534753</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
       <c r="B4">
-        <v>3.4626723821525207E-2</v>
+        <v>3.3835160913421418E-2</v>
       </c>
       <c r="C4">
-        <v>5.6690773107366588E-2</v>
+        <v>5.7347226095890602E-2</v>
       </c>
       <c r="D4">
-        <v>7.1990697736201481E-2</v>
+        <v>7.1955365095613844E-2</v>
       </c>
       <c r="E4">
-        <v>0.11848926756304851</v>
+        <v>0.1210045405201913</v>
       </c>
       <c r="F4">
-        <v>0.13720489882205161</v>
+        <v>0.1353207649946899</v>
       </c>
       <c r="G4">
-        <v>0.14487462125337741</v>
+        <v>0.14368813654030491</v>
       </c>
       <c r="H4">
-        <v>0.13902906818872601</v>
+        <v>0.13915089479142931</v>
       </c>
       <c r="I4">
-        <v>0.17497940989464611</v>
+        <v>0.17450299509745371</v>
       </c>
       <c r="J4">
-        <v>0.2198700881194858</v>
+        <v>0.2209229710468692</v>
       </c>
       <c r="K4">
-        <v>0.32328163851682429</v>
+        <v>0.32828099271014533</v>
       </c>
       <c r="L4">
-        <v>0.37275928117448792</v>
+        <v>0.3740482612367414</v>
       </c>
       <c r="M4">
-        <v>0.3731801330822162</v>
+        <v>0.37721336698789992</v>
       </c>
       <c r="N4">
-        <v>0.37934180794869188</v>
+        <v>0.38511784278724548</v>
       </c>
       <c r="O4">
-        <v>0.40625337447130833</v>
+        <v>0.4095126317084799</v>
       </c>
       <c r="P4">
-        <v>0.41553642835999222</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+        <v>0.42019086225146179</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
       <c r="B5">
-        <v>2.9182653234627098E-2</v>
+        <v>2.7997208810666922E-2</v>
       </c>
       <c r="C5">
-        <v>5.8256643629826972E-2</v>
+        <v>5.5953494258544567E-2</v>
       </c>
       <c r="D5">
-        <v>9.5811353348929762E-2</v>
+        <v>9.666350795220402E-2</v>
       </c>
       <c r="E5">
-        <v>0.12959754436177739</v>
+        <v>0.13173385518987021</v>
       </c>
       <c r="F5">
-        <v>0.17876279556177821</v>
+        <v>0.18255611676881039</v>
       </c>
       <c r="G5">
-        <v>0.203965223015767</v>
+        <v>0.20680134473018191</v>
       </c>
       <c r="H5">
-        <v>0.2322094681234754</v>
+        <v>0.23870663597831299</v>
       </c>
       <c r="I5">
-        <v>0.27261732542475647</v>
+        <v>0.28178619802855598</v>
       </c>
       <c r="J5">
-        <v>0.3258682215114887</v>
+        <v>0.34111623965771698</v>
       </c>
       <c r="K5">
-        <v>0.34462824425406452</v>
+        <v>0.36377592529893887</v>
       </c>
       <c r="L5">
-        <v>0.37894905659611972</v>
+        <v>0.40170405732650921</v>
       </c>
       <c r="M5">
-        <v>0.413836656726562</v>
+        <v>0.42496192412130263</v>
       </c>
       <c r="N5">
-        <v>0.44798413701076029</v>
+        <v>0.45999040467768448</v>
       </c>
       <c r="O5">
-        <v>0.4817375982588038</v>
+        <v>0.50068931960293961</v>
       </c>
       <c r="P5">
-        <v>0.48160712518924381</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+        <v>0.49909628960712249</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>20</v>
       </c>
       <c r="B6">
-        <v>2.8505398897996529E-2</v>
+        <v>2.7009047170418961E-2</v>
       </c>
       <c r="C6">
-        <v>5.6529818066409672E-2</v>
+        <v>5.3764413713701553E-2</v>
       </c>
       <c r="D6">
-        <v>8.0924120485369788E-2</v>
+        <v>7.7937895082812791E-2</v>
       </c>
       <c r="E6">
-        <v>0.13806684632974381</v>
+        <v>0.1333553445852492</v>
       </c>
       <c r="F6">
-        <v>0.1648252014970468</v>
+        <v>0.16625524551126589</v>
       </c>
       <c r="G6">
-        <v>0.21885956888666841</v>
+        <v>0.21825475569437311</v>
       </c>
       <c r="H6">
-        <v>0.23755961504258749</v>
+        <v>0.23292299835345051</v>
       </c>
       <c r="I6">
-        <v>0.28532330233152697</v>
+        <v>0.28259168867593631</v>
       </c>
       <c r="J6">
-        <v>0.30621537530900639</v>
+        <v>0.2995841601293</v>
       </c>
       <c r="K6">
-        <v>0.32756757726236801</v>
+        <v>0.32134370431339271</v>
       </c>
       <c r="L6">
-        <v>0.38006970564548198</v>
+        <v>0.37401797481435273</v>
       </c>
       <c r="M6">
-        <v>0.45660021141444362</v>
+        <v>0.44364121746448643</v>
       </c>
       <c r="N6">
-        <v>0.51436553030916943</v>
+        <v>0.50465332639574578</v>
       </c>
       <c r="O6">
-        <v>0.53359128326651617</v>
+        <v>0.52581031544180679</v>
       </c>
       <c r="P6">
-        <v>0.50419571167217714</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+        <v>0.50004623973548978</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
       <c r="B7">
-        <v>3.5866011181009738E-2</v>
+        <v>3.6022600216342571E-2</v>
       </c>
       <c r="C7">
-        <v>5.7643930792930731E-2</v>
+        <v>5.7370290730546232E-2</v>
       </c>
       <c r="D7">
-        <v>8.7339645728151005E-2</v>
+        <v>8.7446815292332114E-2</v>
       </c>
       <c r="E7">
-        <v>7.4999198942109158E-2</v>
+        <v>7.5654245246991714E-2</v>
       </c>
       <c r="F7">
-        <v>9.7216622471452574E-2</v>
+        <v>0.1007763964630323</v>
       </c>
       <c r="G7">
-        <v>9.2279879739023185E-2</v>
+        <v>9.4846690029648406E-2</v>
       </c>
       <c r="H7">
-        <v>0.12088906861461279</v>
+        <v>0.12436520004798519</v>
       </c>
       <c r="I7">
-        <v>0.152841077832473</v>
+        <v>0.15607602382392771</v>
       </c>
       <c r="J7">
-        <v>0.1881003437254247</v>
+        <v>0.18982921855027701</v>
       </c>
       <c r="K7">
-        <v>0.21034423202885361</v>
+        <v>0.21653535916014441</v>
       </c>
       <c r="L7">
-        <v>0.30068324731838258</v>
+        <v>0.30894855810543292</v>
       </c>
       <c r="M7">
-        <v>0.30500465037069419</v>
+        <v>0.31157862830252819</v>
       </c>
       <c r="N7">
-        <v>0.29940815994232212</v>
+        <v>0.30497198293578542</v>
       </c>
       <c r="O7">
-        <v>0.30656993252008208</v>
+        <v>0.313666997281558</v>
       </c>
       <c r="P7">
-        <v>0.31870952600562952</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+        <v>0.32647873461778842</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>22</v>
       </c>
       <c r="B8">
-        <v>3.1656110093336347E-2</v>
+        <v>3.0897142413666919E-2</v>
       </c>
       <c r="C8">
-        <v>5.5398818866176702E-2</v>
+        <v>5.4242656818098138E-2</v>
       </c>
       <c r="D8">
-        <v>9.0978216183034366E-2</v>
+        <v>9.4331657716207551E-2</v>
       </c>
       <c r="E8">
-        <v>0.1113029412236104</v>
+        <v>0.1160299866925675</v>
       </c>
       <c r="F8">
-        <v>0.1167710474903834</v>
+        <v>0.1204660997687093</v>
       </c>
       <c r="G8">
-        <v>0.162432385877051</v>
+        <v>0.169002726611995</v>
       </c>
       <c r="H8">
-        <v>0.1793201948750324</v>
+        <v>0.18616796856663029</v>
       </c>
       <c r="I8">
-        <v>0.19401826680006901</v>
+        <v>0.2016740095290914</v>
       </c>
       <c r="J8">
-        <v>0.28402970658883109</v>
+        <v>0.29167098598810831</v>
       </c>
       <c r="K8">
-        <v>0.339345805134115</v>
+        <v>0.35554627651278259</v>
       </c>
       <c r="L8">
-        <v>0.35072886920609381</v>
+        <v>0.36771941173088779</v>
       </c>
       <c r="M8">
-        <v>0.3498275978398438</v>
+        <v>0.36163615013531941</v>
       </c>
       <c r="N8">
-        <v>0.34144368119083668</v>
+        <v>0.35348104855410822</v>
       </c>
       <c r="O8">
-        <v>0.37347398943411619</v>
+        <v>0.38730211218242189</v>
       </c>
       <c r="P8">
-        <v>0.37714309418425329</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+        <v>0.39242558042129339</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>23</v>
       </c>
       <c r="B9">
-        <v>3.0292893143503089E-2</v>
+        <v>3.1398802445218137E-2</v>
       </c>
       <c r="C9">
-        <v>5.4388932630927311E-2</v>
+        <v>5.6809214116957329E-2</v>
       </c>
       <c r="D9">
-        <v>9.4493540923012209E-2</v>
+        <v>9.5488525582447914E-2</v>
       </c>
       <c r="E9">
-        <v>0.1160608130141603</v>
+        <v>0.1174690279726488</v>
       </c>
       <c r="F9">
-        <v>0.11626676441259511</v>
+        <v>0.1194560451002902</v>
       </c>
       <c r="G9">
-        <v>0.1566047715675406</v>
+        <v>0.15920252678419619</v>
       </c>
       <c r="H9">
-        <v>0.1741674703151567</v>
+        <v>0.17446370263871491</v>
       </c>
       <c r="I9">
-        <v>0.17019662483386161</v>
+        <v>0.1734752962655309</v>
       </c>
       <c r="J9">
-        <v>0.2278898558827965</v>
+        <v>0.2309430433005161</v>
       </c>
       <c r="K9">
-        <v>0.28655124137197702</v>
+        <v>0.28317993354695592</v>
       </c>
       <c r="L9">
-        <v>0.31583203345648819</v>
+        <v>0.31371036468482483</v>
       </c>
       <c r="M9">
-        <v>0.30501319054323389</v>
+        <v>0.30325351464789591</v>
       </c>
       <c r="N9">
-        <v>0.28393423706841492</v>
+        <v>0.28230868614668958</v>
       </c>
       <c r="O9">
-        <v>0.30377095350088112</v>
+        <v>0.30054850551968598</v>
       </c>
       <c r="P9">
-        <v>0.32745792744882579</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+        <v>0.3267697862338213</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>24</v>
       </c>
       <c r="B10">
-        <v>3.136713371359473E-2</v>
+        <v>3.07099306947668E-2</v>
       </c>
       <c r="C10">
-        <v>5.4020738006749953E-2</v>
+        <v>5.3967833842007477E-2</v>
       </c>
       <c r="D10">
-        <v>9.4039201639784298E-2</v>
+        <v>8.7889837316044495E-2</v>
       </c>
       <c r="E10">
-        <v>0.1137000649646113</v>
+        <v>0.10824391812876449</v>
       </c>
       <c r="F10">
-        <v>0.1196685692755758</v>
+        <v>0.112808644911878</v>
       </c>
       <c r="G10">
-        <v>0.15965876816326641</v>
+        <v>0.1532318940183035</v>
       </c>
       <c r="H10">
-        <v>0.17493354282233589</v>
+        <v>0.1688386859905511</v>
       </c>
       <c r="I10">
-        <v>0.16992839379424171</v>
+        <v>0.16333005807855339</v>
       </c>
       <c r="J10">
-        <v>0.2274961210184793</v>
+        <v>0.2180106467024332</v>
       </c>
       <c r="K10">
-        <v>0.28840862216461549</v>
+        <v>0.2745525029926193</v>
       </c>
       <c r="L10">
-        <v>0.31205683042021792</v>
+        <v>0.3040626598141567</v>
       </c>
       <c r="M10">
-        <v>0.30079231386884658</v>
+        <v>0.29290162908173789</v>
       </c>
       <c r="N10">
-        <v>0.2754308757814794</v>
+        <v>0.2712437879549654</v>
       </c>
       <c r="O10">
-        <v>0.28697112039185257</v>
+        <v>0.28308499100808898</v>
       </c>
       <c r="P10">
-        <v>0.30849966453057193</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+        <v>0.30907407504145878</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>25</v>
       </c>
       <c r="B11">
-        <v>3.0881275613137471E-2</v>
+        <v>3.1925983526622959E-2</v>
       </c>
       <c r="C11">
-        <v>5.5754469186025002E-2</v>
+        <v>5.5189315978159681E-2</v>
       </c>
       <c r="D11">
-        <v>9.2875201045702904E-2</v>
+        <v>9.2413432484905633E-2</v>
       </c>
       <c r="E11">
-        <v>0.1141621526763308</v>
+        <v>0.11421672311342281</v>
       </c>
       <c r="F11">
-        <v>0.11675860338332079</v>
+        <v>0.12039094774123769</v>
       </c>
       <c r="G11">
-        <v>0.15973497011094559</v>
+        <v>0.16335506690685961</v>
       </c>
       <c r="H11">
-        <v>0.17659396286235229</v>
+        <v>0.1796502889795375</v>
       </c>
       <c r="I11">
-        <v>0.16962720824778579</v>
+        <v>0.17354662084242431</v>
       </c>
       <c r="J11">
-        <v>0.22927701953063989</v>
+        <v>0.22963808208622349</v>
       </c>
       <c r="K11">
-        <v>0.28106969936024689</v>
+        <v>0.28631023474626971</v>
       </c>
       <c r="L11">
-        <v>0.29910367029253487</v>
+        <v>0.30532151305952743</v>
       </c>
       <c r="M11">
-        <v>0.2889607299563749</v>
+        <v>0.29661543444897082</v>
       </c>
       <c r="N11">
-        <v>0.28201848853831379</v>
+        <v>0.28619145891904357</v>
       </c>
       <c r="O11">
-        <v>0.31103508559858711</v>
+        <v>0.31909102126610073</v>
       </c>
       <c r="P11">
-        <v>0.30218171577371411</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+        <v>0.30918318658611232</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>26</v>
       </c>
       <c r="B12">
-        <v>2.752362209971659E-2</v>
+        <v>2.9661324286891388E-2</v>
       </c>
       <c r="C12">
-        <v>5.3956338259884329E-2</v>
+        <v>5.6496265336447797E-2</v>
       </c>
       <c r="D12">
-        <v>9.5690416646056375E-2</v>
+        <v>9.7736703769851885E-2</v>
       </c>
       <c r="E12">
-        <v>0.13178571287538551</v>
+        <v>0.13594538824357841</v>
       </c>
       <c r="F12">
-        <v>0.15583201892766149</v>
+        <v>0.15857131834033211</v>
       </c>
       <c r="G12">
-        <v>0.18121217095474421</v>
+        <v>0.18211699344292959</v>
       </c>
       <c r="H12">
-        <v>0.2067469923212992</v>
+        <v>0.20496715380200631</v>
       </c>
       <c r="I12">
-        <v>0.2439024571006938</v>
+        <v>0.23901824138414049</v>
       </c>
       <c r="J12">
-        <v>0.27284054366922689</v>
+        <v>0.27089308051558808</v>
       </c>
       <c r="K12">
-        <v>0.30360395277249219</v>
+        <v>0.30195673011927221</v>
       </c>
       <c r="L12">
-        <v>0.35706440240430659</v>
+        <v>0.34749677835077603</v>
       </c>
       <c r="M12">
-        <v>0.40129951069135578</v>
+        <v>0.39673577007425481</v>
       </c>
       <c r="N12">
-        <v>0.42344605917886441</v>
+        <v>0.41233629412007028</v>
       </c>
       <c r="O12">
-        <v>0.45213783567318988</v>
+        <v>0.44606503293488381</v>
       </c>
       <c r="P12">
-        <v>0.47040151152389498</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+        <v>0.45898545807144892</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>27</v>
       </c>
       <c r="B13">
-        <v>3.07906431750169E-2</v>
+        <v>3.170474607602225E-2</v>
       </c>
       <c r="C13">
-        <v>6.6631909736681094E-2</v>
+        <v>6.9197976728660904E-2</v>
       </c>
       <c r="D13">
-        <v>0.1011684942720044</v>
+        <v>0.1059472876886051</v>
       </c>
       <c r="E13">
-        <v>0.1202521725590073</v>
+        <v>0.1247590111767138</v>
       </c>
       <c r="F13">
-        <v>0.1622587788109229</v>
+        <v>0.16422122750767451</v>
       </c>
       <c r="G13">
-        <v>0.20420834770452961</v>
+        <v>0.20819336926048129</v>
       </c>
       <c r="H13">
-        <v>0.23035026117700549</v>
+        <v>0.23351286415742631</v>
       </c>
       <c r="I13">
-        <v>0.2751731168031859</v>
+        <v>0.27876379563217812</v>
       </c>
       <c r="J13">
-        <v>0.30828116985245518</v>
+        <v>0.31381830928317561</v>
       </c>
       <c r="K13">
-        <v>0.35382609652994679</v>
+        <v>0.35854654115465828</v>
       </c>
       <c r="L13">
-        <v>0.373017610569849</v>
+        <v>0.37862887578745469</v>
       </c>
       <c r="M13">
-        <v>0.38759688190269642</v>
+        <v>0.39435305452412878</v>
       </c>
       <c r="N13">
-        <v>0.40821878964843372</v>
+        <v>0.41739190094905759</v>
       </c>
       <c r="O13">
-        <v>0.43594336066697542</v>
+        <v>0.44263262849782548</v>
       </c>
       <c r="P13">
-        <v>0.47601373470463121</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+        <v>0.48905609869936478</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>28</v>
       </c>
       <c r="B14">
-        <v>3.3736474727309777E-2</v>
+        <v>3.2805884986460698E-2</v>
       </c>
       <c r="C14">
-        <v>5.5286927231505738E-2</v>
+        <v>5.4827226926406403E-2</v>
       </c>
       <c r="D14">
-        <v>8.707437046110722E-2</v>
+        <v>8.4014959724313387E-2</v>
       </c>
       <c r="E14">
-        <v>7.4274092191196073E-2</v>
+        <v>7.119241762678985E-2</v>
       </c>
       <c r="F14">
-        <v>9.7821117561969984E-2</v>
+        <v>9.3986169518756824E-2</v>
       </c>
       <c r="G14">
-        <v>9.3421373850180789E-2</v>
+        <v>9.2692717582738782E-2</v>
       </c>
       <c r="H14">
-        <v>0.1186779733202336</v>
+        <v>0.1131105137457727</v>
       </c>
       <c r="I14">
-        <v>0.14005411992605821</v>
+        <v>0.13921409421632239</v>
       </c>
       <c r="J14">
-        <v>0.1685834955896087</v>
+        <v>0.168241085282228</v>
       </c>
       <c r="K14">
-        <v>0.18173053426741251</v>
+        <v>0.184395798484983</v>
       </c>
       <c r="L14">
-        <v>0.27804166804788227</v>
+        <v>0.27867584016324709</v>
       </c>
       <c r="M14">
-        <v>0.2996547930557969</v>
+        <v>0.29768163543629628</v>
       </c>
       <c r="N14">
-        <v>0.28621162402805839</v>
+        <v>0.28753675684441882</v>
       </c>
       <c r="O14">
-        <v>0.28298417524663833</v>
+        <v>0.28010844307852117</v>
       </c>
       <c r="P14">
-        <v>0.27319755893388559</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+        <v>0.2701702388271342</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15">
-        <v>3.5349091781406938E-2</v>
+        <v>3.7055999075655773E-2</v>
       </c>
       <c r="C15">
-        <v>5.7453665137121017E-2</v>
+        <v>5.911018418853714E-2</v>
       </c>
       <c r="D15">
-        <v>8.737849334111869E-2</v>
+        <v>8.6998184689367375E-2</v>
       </c>
       <c r="E15">
-        <v>7.3374154744002329E-2</v>
+        <v>7.5186160397957669E-2</v>
       </c>
       <c r="F15">
-        <v>9.7592728166544074E-2</v>
+        <v>9.8340035355287791E-2</v>
       </c>
       <c r="G15">
-        <v>9.3919475845173017E-2</v>
+        <v>9.5071684829385328E-2</v>
       </c>
       <c r="H15">
-        <v>0.1182363441780528</v>
+        <v>0.1200036904016238</v>
       </c>
       <c r="I15">
-        <v>0.13975236347611161</v>
+        <v>0.14346192317155371</v>
       </c>
       <c r="J15">
-        <v>0.16718621140703219</v>
+        <v>0.16725020840352489</v>
       </c>
       <c r="K15">
-        <v>0.18158753943053221</v>
+        <v>0.18050087985691191</v>
       </c>
       <c r="L15">
-        <v>0.26845316742405723</v>
+        <v>0.26641964931463358</v>
       </c>
       <c r="M15">
-        <v>0.29807887567062441</v>
+        <v>0.29383369884991339</v>
       </c>
       <c r="N15">
-        <v>0.2893278855575292</v>
+        <v>0.28481034095327962</v>
       </c>
       <c r="O15">
-        <v>0.28354313021934358</v>
+        <v>0.27992435687553652</v>
       </c>
       <c r="P15">
-        <v>0.27034236100799092</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+        <v>0.26825852356630048</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16">
-        <v>3.3193299085192092E-2</v>
+        <v>3.1273774190704602E-2</v>
       </c>
       <c r="C16">
-        <v>5.3897978354736642E-2</v>
+        <v>5.3198421484853653E-2</v>
       </c>
       <c r="D16">
-        <v>8.0610150572228312E-2</v>
+        <v>8.3655899144688961E-2</v>
       </c>
       <c r="E16">
-        <v>7.1362640688164891E-2</v>
+        <v>7.3406488608628417E-2</v>
       </c>
       <c r="F16">
-        <v>9.4013453841518713E-2</v>
+        <v>9.5429457066601442E-2</v>
       </c>
       <c r="G16">
-        <v>9.1554810087981831E-2</v>
+        <v>9.053637021085581E-2</v>
       </c>
       <c r="H16">
-        <v>0.1145720371186096</v>
+        <v>0.1150292263061258</v>
       </c>
       <c r="I16">
-        <v>0.13819267989054129</v>
+        <v>0.13579429965025669</v>
       </c>
       <c r="J16">
-        <v>0.16512434331757131</v>
+        <v>0.16067414887441511</v>
       </c>
       <c r="K16">
-        <v>0.18060884366021371</v>
+        <v>0.17231849702000879</v>
       </c>
       <c r="L16">
-        <v>0.26553611009180389</v>
+        <v>0.25596624211363428</v>
       </c>
       <c r="M16">
-        <v>0.28847660876471909</v>
+        <v>0.27854403163233482</v>
       </c>
       <c r="N16">
-        <v>0.28207693586827909</v>
+        <v>0.26925748105370079</v>
       </c>
       <c r="O16">
-        <v>0.27993714255214769</v>
+        <v>0.26709329569691659</v>
       </c>
       <c r="P16">
-        <v>0.26988212971486469</v>
+        <v>0.25662155716756091</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
@@ -1432,49 +1400,49 @@
         <v>31</v>
       </c>
       <c r="B17">
-        <v>3.195608310435355E-2</v>
+        <v>3.4182962961803398E-2</v>
       </c>
       <c r="C17">
-        <v>5.4198456085746798E-2</v>
+        <v>5.6313682296376337E-2</v>
       </c>
       <c r="D17">
-        <v>8.5273835573760004E-2</v>
+        <v>8.3578562669378353E-2</v>
       </c>
       <c r="E17">
-        <v>7.506785341322908E-2</v>
+        <v>7.2365069076051003E-2</v>
       </c>
       <c r="F17">
-        <v>9.9414483292552425E-2</v>
+        <v>9.5687789869301709E-2</v>
       </c>
       <c r="G17">
-        <v>9.3692882941488365E-2</v>
+        <v>9.1230631409441543E-2</v>
       </c>
       <c r="H17">
-        <v>0.11804652890607981</v>
+        <v>0.11340174598757249</v>
       </c>
       <c r="I17">
-        <v>0.139300579367864</v>
+        <v>0.133752161891149</v>
       </c>
       <c r="J17">
-        <v>0.16696959597158809</v>
+        <v>0.15976180409365709</v>
       </c>
       <c r="K17">
-        <v>0.17968515865926329</v>
+        <v>0.1702070174195576</v>
       </c>
       <c r="L17">
-        <v>0.26842046598856723</v>
+        <v>0.2509823317032942</v>
       </c>
       <c r="M17">
-        <v>0.29237460529688508</v>
+        <v>0.27442878586117508</v>
       </c>
       <c r="N17">
-        <v>0.27774911910238309</v>
+        <v>0.2607686553655828</v>
       </c>
       <c r="O17">
-        <v>0.27379691467981521</v>
+        <v>0.2569325460475218</v>
       </c>
       <c r="P17">
-        <v>0.25957484107636042</v>
+        <v>0.24628498562254589</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
@@ -1482,49 +1450,49 @@
         <v>32</v>
       </c>
       <c r="B18">
-        <v>2.8187121833311402E-2</v>
+        <v>3.097309961227768E-2</v>
       </c>
       <c r="C18">
-        <v>5.6269868080533358E-2</v>
+        <v>5.9617912579523653E-2</v>
       </c>
       <c r="D18">
-        <v>9.9126731900066711E-2</v>
+        <v>0.1081564127215817</v>
       </c>
       <c r="E18">
-        <v>0.12786086408271199</v>
+        <v>0.1381901216292202</v>
       </c>
       <c r="F18">
-        <v>0.15557903658406211</v>
+        <v>0.16440548633513419</v>
       </c>
       <c r="G18">
-        <v>0.20375777391396069</v>
+        <v>0.21148252459514141</v>
       </c>
       <c r="H18">
-        <v>0.20616511484823971</v>
+        <v>0.21667769040022769</v>
       </c>
       <c r="I18">
-        <v>0.23521691747591941</v>
+        <v>0.24030590762613779</v>
       </c>
       <c r="J18">
-        <v>0.25577673302341281</v>
+        <v>0.26117470874201909</v>
       </c>
       <c r="K18">
-        <v>0.27430975054658652</v>
+        <v>0.28022703968568241</v>
       </c>
       <c r="L18">
-        <v>0.29796846425822487</v>
+        <v>0.29923261859048927</v>
       </c>
       <c r="M18">
-        <v>0.33243076866180071</v>
+        <v>0.33636902939234697</v>
       </c>
       <c r="N18">
-        <v>0.3502904496747844</v>
+        <v>0.3546768881254726</v>
       </c>
       <c r="O18">
-        <v>0.3838151764706208</v>
+        <v>0.38521191403923588</v>
       </c>
       <c r="P18">
-        <v>0.39473933217000778</v>
+        <v>0.39059484059045901</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
@@ -1532,49 +1500,49 @@
         <v>33</v>
       </c>
       <c r="B19">
-        <v>2.8413787898728841E-2</v>
+        <v>2.8257622060291029E-2</v>
       </c>
       <c r="C19">
-        <v>5.6437426694557091E-2</v>
+        <v>5.596782325997518E-2</v>
       </c>
       <c r="D19">
-        <v>8.3246398194787408E-2</v>
+        <v>8.1203568323561459E-2</v>
       </c>
       <c r="E19">
-        <v>0.13649803339382771</v>
+        <v>0.13300158158091049</v>
       </c>
       <c r="F19">
-        <v>0.1602885919161022</v>
+        <v>0.16137983831161859</v>
       </c>
       <c r="G19">
-        <v>0.1801378719177387</v>
+        <v>0.17954785483274949</v>
       </c>
       <c r="H19">
-        <v>0.19461066062527621</v>
+        <v>0.19482568925606919</v>
       </c>
       <c r="I19">
-        <v>0.22673088584291379</v>
+        <v>0.23193476420883671</v>
       </c>
       <c r="J19">
-        <v>0.24431760948364981</v>
+        <v>0.24773307660402061</v>
       </c>
       <c r="K19">
-        <v>0.24753438142051401</v>
+        <v>0.25188923162884891</v>
       </c>
       <c r="L19">
-        <v>0.29096754026782978</v>
+        <v>0.29471343013522799</v>
       </c>
       <c r="M19">
-        <v>0.32977644705713471</v>
+        <v>0.331370101832272</v>
       </c>
       <c r="N19">
-        <v>0.34630541179945568</v>
+        <v>0.34839369274159088</v>
       </c>
       <c r="O19">
-        <v>0.36525827227737601</v>
+        <v>0.36632733266732082</v>
       </c>
       <c r="P19">
-        <v>0.36893160853721307</v>
+        <v>0.36864028503188923</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
@@ -1582,49 +1550,49 @@
         <v>34</v>
       </c>
       <c r="B20">
-        <v>2.5818283405496079E-2</v>
+        <v>2.668009558133189E-2</v>
       </c>
       <c r="C20">
-        <v>4.9019385473160433E-2</v>
+        <v>4.8858097121170063E-2</v>
       </c>
       <c r="D20">
-        <v>8.8776563941487696E-2</v>
+        <v>8.5374085573669989E-2</v>
       </c>
       <c r="E20">
-        <v>0.14791064230250989</v>
+        <v>0.14843325113547129</v>
       </c>
       <c r="F20">
-        <v>0.173451268457844</v>
+        <v>0.1757272004587643</v>
       </c>
       <c r="G20">
-        <v>0.16694667287382431</v>
+        <v>0.17214650304561871</v>
       </c>
       <c r="H20">
-        <v>0.176818705209522</v>
+        <v>0.17692254986391301</v>
       </c>
       <c r="I20">
-        <v>0.21061959333675359</v>
+        <v>0.2126532037305453</v>
       </c>
       <c r="J20">
-        <v>0.21589426680033111</v>
+        <v>0.21667236129854001</v>
       </c>
       <c r="K20">
-        <v>0.23227533813331161</v>
+        <v>0.23277726310508021</v>
       </c>
       <c r="L20">
-        <v>0.26708449995626971</v>
+        <v>0.26594627513318347</v>
       </c>
       <c r="M20">
-        <v>0.31403285601316971</v>
+        <v>0.31210144681278978</v>
       </c>
       <c r="N20">
-        <v>0.33901246290291981</v>
+        <v>0.33147974890217918</v>
       </c>
       <c r="O20">
-        <v>0.33052250221447371</v>
+        <v>0.31898752856792378</v>
       </c>
       <c r="P20">
-        <v>0.3434169902174411</v>
+        <v>0.33446043879921988</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
@@ -1632,49 +1600,49 @@
         <v>35</v>
       </c>
       <c r="B21">
-        <v>4.1515397374693008E-2</v>
+        <v>3.9939070161663037E-2</v>
       </c>
       <c r="C21">
-        <v>4.0242196956848719E-2</v>
+        <v>3.9581175112931688E-2</v>
       </c>
       <c r="D21">
-        <v>7.3898442831354716E-2</v>
+        <v>7.1167319995483314E-2</v>
       </c>
       <c r="E21">
-        <v>9.3953041335664067E-2</v>
+        <v>9.1862032778225577E-2</v>
       </c>
       <c r="F21">
-        <v>0.15159127538370271</v>
+        <v>0.1448565897630377</v>
       </c>
       <c r="G21">
-        <v>0.20495397510967719</v>
+        <v>0.1939183178913213</v>
       </c>
       <c r="H21">
-        <v>0.29326827002336842</v>
+        <v>0.27798995434779161</v>
       </c>
       <c r="I21">
-        <v>0.33875755443772881</v>
+        <v>0.32178150340247219</v>
       </c>
       <c r="J21">
-        <v>0.35837668640341008</v>
+        <v>0.34588021178096789</v>
       </c>
       <c r="K21">
-        <v>0.39367337225128829</v>
+        <v>0.37946784444360743</v>
       </c>
       <c r="L21">
-        <v>0.44374622937842811</v>
+        <v>0.43072429141710872</v>
       </c>
       <c r="M21">
-        <v>0.49604799542613359</v>
+        <v>0.48171067475047258</v>
       </c>
       <c r="N21">
-        <v>0.55598241069757504</v>
+        <v>0.54476683926382208</v>
       </c>
       <c r="O21">
-        <v>0.63221230774925019</v>
+        <v>0.62539712747386345</v>
       </c>
       <c r="P21">
-        <v>0.72069770403353561</v>
+        <v>0.71286714925463435</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
@@ -1682,49 +1650,49 @@
         <v>36</v>
       </c>
       <c r="B22">
-        <v>4.2183574642805921E-2</v>
+        <v>4.0965103877323439E-2</v>
       </c>
       <c r="C22">
-        <v>4.0818417378273741E-2</v>
+        <v>3.9416269418693917E-2</v>
       </c>
       <c r="D22">
-        <v>6.9933504293792081E-2</v>
+        <v>6.9621141227814043E-2</v>
       </c>
       <c r="E22">
-        <v>8.805650612099214E-2</v>
+        <v>9.198819093919175E-2</v>
       </c>
       <c r="F22">
-        <v>0.14540139442502359</v>
+        <v>0.15087173250902949</v>
       </c>
       <c r="G22">
-        <v>0.1777602022367879</v>
+        <v>0.18316919048106509</v>
       </c>
       <c r="H22">
-        <v>0.27497358461878102</v>
+        <v>0.28162786761958508</v>
       </c>
       <c r="I22">
-        <v>0.3240050615271084</v>
+        <v>0.32904037234454903</v>
       </c>
       <c r="J22">
-        <v>0.34839213879990738</v>
+        <v>0.3587845333324941</v>
       </c>
       <c r="K22">
-        <v>0.37582192884064469</v>
+        <v>0.38440429754457828</v>
       </c>
       <c r="L22">
-        <v>0.43181740610652758</v>
+        <v>0.44090761287995311</v>
       </c>
       <c r="M22">
-        <v>0.48561538802292442</v>
+        <v>0.49313119931031468</v>
       </c>
       <c r="N22">
-        <v>0.53912377933488642</v>
+        <v>0.55259848242403264</v>
       </c>
       <c r="O22">
-        <v>0.61664793761781422</v>
+        <v>0.63454000047862935</v>
       </c>
       <c r="P22">
-        <v>0.68487202724990781</v>
+        <v>0.70799997463910169</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
@@ -1732,49 +1700,49 @@
         <v>37</v>
       </c>
       <c r="B23">
-        <v>2.7477443907157562E-2</v>
+        <v>3.0397571995501971E-2</v>
       </c>
       <c r="C23">
-        <v>9.2526888845313349E-2</v>
+        <v>9.9992594194912687E-2</v>
       </c>
       <c r="D23">
-        <v>0.10015111920973969</v>
+        <v>0.1046897829260638</v>
       </c>
       <c r="E23">
-        <v>9.7388172984773869E-2</v>
+        <v>9.8196678318504094E-2</v>
       </c>
       <c r="F23">
-        <v>0.1642317310191119</v>
+        <v>0.16806614996039421</v>
       </c>
       <c r="G23">
-        <v>0.2596657995664719</v>
+        <v>0.25835894805303139</v>
       </c>
       <c r="H23">
-        <v>0.36381367687714489</v>
+        <v>0.36725056380066229</v>
       </c>
       <c r="I23">
-        <v>0.40733374417405582</v>
+        <v>0.40562710974479238</v>
       </c>
       <c r="J23">
-        <v>0.4821191901129584</v>
+        <v>0.47992522673070098</v>
       </c>
       <c r="K23">
-        <v>0.54729529117577469</v>
+        <v>0.54917911997402968</v>
       </c>
       <c r="L23">
-        <v>0.61585368924204453</v>
+        <v>0.62142819692928319</v>
       </c>
       <c r="M23">
-        <v>0.65462843647802815</v>
+        <v>0.65952977873701646</v>
       </c>
       <c r="N23">
-        <v>0.71127311414868155</v>
+        <v>0.72073287324072177</v>
       </c>
       <c r="O23">
-        <v>0.78221598937391013</v>
+        <v>0.78906502375514354</v>
       </c>
       <c r="P23">
-        <v>0.85694425954659759</v>
+        <v>0.86505560396038672</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
@@ -1782,49 +1750,49 @@
         <v>38</v>
       </c>
       <c r="B24">
-        <v>6.5818295223828455E-2</v>
+        <v>6.6798312763786255E-2</v>
       </c>
       <c r="C24">
-        <v>0.1894443706729152</v>
+        <v>0.18428319925134509</v>
       </c>
       <c r="D24">
-        <v>0.1884665987371206</v>
+        <v>0.18920825807653041</v>
       </c>
       <c r="E24">
-        <v>0.31596558065300751</v>
+        <v>0.32597110908788191</v>
       </c>
       <c r="F24">
-        <v>0.76466434238833769</v>
+        <v>0.76454089022068561</v>
       </c>
       <c r="G24">
-        <v>0.72359703226142669</v>
+        <v>0.72020956438300121</v>
       </c>
       <c r="H24">
-        <v>0.83575531543303172</v>
+        <v>0.83100402419006136</v>
       </c>
       <c r="I24">
-        <v>0.94482310818647131</v>
+        <v>0.93506693453350997</v>
       </c>
       <c r="J24">
-        <v>1.081839030401007</v>
+        <v>1.051833676755737</v>
       </c>
       <c r="K24">
-        <v>1.1670495152110001</v>
+        <v>1.146153466702593</v>
       </c>
       <c r="L24">
-        <v>1.261539752045566</v>
+        <v>1.239786530951928</v>
       </c>
       <c r="M24">
-        <v>1.3291058216418461</v>
+        <v>1.311411095654339</v>
       </c>
       <c r="N24">
-        <v>1.3715649472627729</v>
+        <v>1.3477329101665969</v>
       </c>
       <c r="O24">
-        <v>1.4406207089283869</v>
+        <v>1.4237247095890231</v>
       </c>
       <c r="P24">
-        <v>1.4822960767543141</v>
+        <v>1.4600015641488859</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
@@ -1832,49 +1800,49 @@
         <v>39</v>
       </c>
       <c r="B25">
-        <v>8.716431692228116E-2</v>
+        <v>8.6683236440662767E-2</v>
       </c>
       <c r="C25">
-        <v>0.1929319718607983</v>
+        <v>0.18514037076025419</v>
       </c>
       <c r="D25">
-        <v>0.26809804163788209</v>
+        <v>0.25934365329225989</v>
       </c>
       <c r="E25">
-        <v>0.45015031041551318</v>
+        <v>0.43689045627997553</v>
       </c>
       <c r="F25">
-        <v>0.59431341938281912</v>
+        <v>0.58908877839460949</v>
       </c>
       <c r="G25">
-        <v>0.78634870360262776</v>
+        <v>0.78080673708529869</v>
       </c>
       <c r="H25">
-        <v>1.0215051745840711</v>
+        <v>1.0053443974405829</v>
       </c>
       <c r="I25">
-        <v>1.156014589471078</v>
+        <v>1.135323446148468</v>
       </c>
       <c r="J25">
-        <v>1.216781525245024</v>
+        <v>1.1898749467764469</v>
       </c>
       <c r="K25">
-        <v>1.265966352218223</v>
+        <v>1.236281875332391</v>
       </c>
       <c r="L25">
-        <v>1.4025786630845389</v>
+        <v>1.384911449944757</v>
       </c>
       <c r="M25">
-        <v>1.533549435643258</v>
+        <v>1.5286023064766621</v>
       </c>
       <c r="N25">
-        <v>1.6540862754360359</v>
+        <v>1.655983711735179</v>
       </c>
       <c r="O25">
-        <v>1.704697292199957</v>
+        <v>1.7014702503938419</v>
       </c>
       <c r="P25">
-        <v>1.7473115886877819</v>
+        <v>1.740115060772385</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
@@ -1882,49 +1850,49 @@
         <v>40</v>
       </c>
       <c r="B26">
-        <v>6.531513156096222E-2</v>
+        <v>5.9628753026859549E-2</v>
       </c>
       <c r="C26">
-        <v>0.12796842728415009</v>
+        <v>0.1154776861273364</v>
       </c>
       <c r="D26">
-        <v>0.14548618817400491</v>
+        <v>0.13910615033283719</v>
       </c>
       <c r="E26">
-        <v>0.28561959774105922</v>
+        <v>0.27324726665237942</v>
       </c>
       <c r="F26">
-        <v>0.42619606819946498</v>
+        <v>0.42797089465029431</v>
       </c>
       <c r="G26">
-        <v>0.50854443508374758</v>
+        <v>0.51331347675924233</v>
       </c>
       <c r="H26">
-        <v>0.63734589994066504</v>
+        <v>0.63467501721960196</v>
       </c>
       <c r="I26">
-        <v>0.62817890116917108</v>
+        <v>0.61485766771425165</v>
       </c>
       <c r="J26">
-        <v>0.61410563224427217</v>
+        <v>0.59918075040660379</v>
       </c>
       <c r="K26">
-        <v>0.6123553052175148</v>
+        <v>0.60398837093147362</v>
       </c>
       <c r="L26">
-        <v>0.80668588004319408</v>
+        <v>0.78916149662437729</v>
       </c>
       <c r="M26">
-        <v>1.017823668770508</v>
+        <v>1.0134891754090221</v>
       </c>
       <c r="N26">
-        <v>1.00940386618861</v>
+        <v>1.001528149196262</v>
       </c>
       <c r="O26">
-        <v>1.078071927632037</v>
+        <v>1.083863552391475</v>
       </c>
       <c r="P26">
-        <v>1.115834769145821</v>
+        <v>1.125439844697562</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
@@ -1932,49 +1900,49 @@
         <v>41</v>
       </c>
       <c r="B27">
-        <v>6.9728858669922372E-2</v>
+        <v>7.0947176491258077E-2</v>
       </c>
       <c r="C27">
-        <v>0.1236868300339974</v>
+        <v>0.1224220831972465</v>
       </c>
       <c r="D27">
-        <v>0.32941120828830339</v>
+        <v>0.32260044708063079</v>
       </c>
       <c r="E27">
-        <v>0.29963712388504471</v>
+        <v>0.30084860904508842</v>
       </c>
       <c r="F27">
-        <v>0.51172417589658159</v>
+        <v>0.50877453192471256</v>
       </c>
       <c r="G27">
-        <v>0.54262680681410003</v>
+        <v>0.55007550572887332</v>
       </c>
       <c r="H27">
-        <v>0.51290713010928091</v>
+        <v>0.5179943219539177</v>
       </c>
       <c r="I27">
-        <v>0.56171770207421501</v>
+        <v>0.5651019559800865</v>
       </c>
       <c r="J27">
-        <v>0.72303723150239807</v>
+        <v>0.7222263511741227</v>
       </c>
       <c r="K27">
-        <v>0.82179130549845747</v>
+        <v>0.82229581804146079</v>
       </c>
       <c r="L27">
-        <v>0.91947885885104175</v>
+        <v>0.91905283522709258</v>
       </c>
       <c r="M27">
-        <v>1.0548106742265451</v>
+        <v>1.0344182927315171</v>
       </c>
       <c r="N27">
-        <v>1.0054874620251359</v>
+        <v>0.98828676582923092</v>
       </c>
       <c r="O27">
-        <v>1.1339582377606121</v>
+        <v>1.1191702371540131</v>
       </c>
       <c r="P27">
-        <v>1.1954089198088551</v>
+        <v>1.180940013417153</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
@@ -1982,49 +1950,49 @@
         <v>42</v>
       </c>
       <c r="B28">
-        <v>2.4014683257267851E-2</v>
+        <v>2.5089577855378801E-2</v>
       </c>
       <c r="C28">
-        <v>4.3169912634025587E-2</v>
+        <v>4.3916137786365383E-2</v>
       </c>
       <c r="D28">
-        <v>5.9137569598546318E-2</v>
+        <v>6.144457197386255E-2</v>
       </c>
       <c r="E28">
-        <v>6.2314097659704533E-2</v>
+        <v>6.3048502357768599E-2</v>
       </c>
       <c r="F28">
-        <v>0.1002194046130449</v>
+        <v>0.1013637141551164</v>
       </c>
       <c r="G28">
-        <v>0.12638234137991189</v>
+        <v>0.1242334976231045</v>
       </c>
       <c r="H28">
-        <v>0.1424890782745164</v>
+        <v>0.14511928971709229</v>
       </c>
       <c r="I28">
-        <v>0.20100513440410969</v>
+        <v>0.1955785627029534</v>
       </c>
       <c r="J28">
-        <v>0.1855249377239154</v>
+        <v>0.1844289048333895</v>
       </c>
       <c r="K28">
-        <v>0.19823003976911049</v>
+        <v>0.19435441137114881</v>
       </c>
       <c r="L28">
-        <v>0.25213691262916599</v>
+        <v>0.25170313323811361</v>
       </c>
       <c r="M28">
-        <v>0.28458154814847242</v>
+        <v>0.28738826720965482</v>
       </c>
       <c r="N28">
-        <v>0.33888156859244573</v>
+        <v>0.34053367301031662</v>
       </c>
       <c r="O28">
-        <v>0.37317620090707931</v>
+        <v>0.37423906429609988</v>
       </c>
       <c r="P28">
-        <v>0.43146793816555129</v>
+        <v>0.42833110533248397</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
@@ -2032,49 +2000,49 @@
         <v>43</v>
       </c>
       <c r="B29">
-        <v>2.271613452267696E-2</v>
+        <v>2.557213430039584E-2</v>
       </c>
       <c r="C29">
-        <v>4.1807677825031808E-2</v>
+        <v>4.5140099914939391E-2</v>
       </c>
       <c r="D29">
-        <v>6.0254421395928397E-2</v>
+        <v>6.1727391396324438E-2</v>
       </c>
       <c r="E29">
-        <v>5.8402099645634808E-2</v>
+        <v>6.0703594714600739E-2</v>
       </c>
       <c r="F29">
-        <v>9.2305930220235477E-2</v>
+        <v>9.1782485839250305E-2</v>
       </c>
       <c r="G29">
-        <v>8.3102493260293175E-2</v>
+        <v>8.4836572703903435E-2</v>
       </c>
       <c r="H29">
-        <v>9.6591996791634438E-2</v>
+        <v>9.7379216613921682E-2</v>
       </c>
       <c r="I29">
-        <v>0.15945914337979381</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0.14395124177270099</v>
+        <v>0.16013406238248029</v>
+      </c>
+      <c r="J29">
+        <v>0.1434437130758425</v>
       </c>
       <c r="K29">
-        <v>0.15875900757826919</v>
+        <v>0.15894053142560849</v>
       </c>
       <c r="L29">
-        <v>0.1742178754637396</v>
+        <v>0.17598030634302331</v>
       </c>
       <c r="M29">
-        <v>0.2013516658764227</v>
+        <v>0.20535971289048441</v>
       </c>
       <c r="N29">
-        <v>0.23768837788522601</v>
+        <v>0.24120362290962749</v>
       </c>
       <c r="O29">
-        <v>0.27002786244546823</v>
+        <v>0.27451929552325288</v>
       </c>
       <c r="P29">
-        <v>0.31167533411535842</v>
+        <v>0.31745491550087568</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
@@ -2082,49 +2050,49 @@
         <v>44</v>
       </c>
       <c r="B30">
-        <v>2.4081580384027749E-2</v>
+        <v>2.3848975728812168E-2</v>
       </c>
       <c r="C30">
-        <v>4.4965715427747188E-2</v>
+        <v>4.5770400261148092E-2</v>
       </c>
       <c r="D30">
-        <v>7.9846914801610214E-2</v>
+        <v>8.0565587709346076E-2</v>
       </c>
       <c r="E30">
-        <v>6.9056745867434932E-2</v>
+        <v>6.8793133810551521E-2</v>
       </c>
       <c r="F30">
-        <v>0.10420435054189769</v>
+        <v>0.10121022376216331</v>
       </c>
       <c r="G30">
-        <v>9.9009900040298415E-2</v>
+        <v>9.8087089833930663E-2</v>
       </c>
       <c r="H30">
-        <v>0.1264400176986139</v>
+        <v>0.1240476998053605</v>
       </c>
       <c r="I30">
-        <v>0.15312923936867179</v>
+        <v>0.15964462276849289</v>
       </c>
       <c r="J30">
-        <v>0.19142750887755389</v>
+        <v>0.19278681141880161</v>
       </c>
       <c r="K30">
-        <v>0.21449691596635401</v>
+        <v>0.2128950895530248</v>
       </c>
       <c r="L30">
-        <v>0.23773935725376449</v>
+        <v>0.23960905946625549</v>
       </c>
       <c r="M30">
-        <v>0.25816208993050788</v>
+        <v>0.25935096371651978</v>
       </c>
       <c r="N30">
-        <v>0.29271349481085829</v>
+        <v>0.29777945234814651</v>
       </c>
       <c r="O30">
-        <v>0.33876641768693122</v>
+        <v>0.34335981096139639</v>
       </c>
       <c r="P30">
-        <v>0.38278230139921587</v>
+        <v>0.38950101848326929</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
@@ -2132,49 +2100,49 @@
         <v>45</v>
       </c>
       <c r="B31">
-        <v>2.118087155163972E-2</v>
+        <v>2.2462716006337868E-2</v>
       </c>
       <c r="C31">
-        <v>4.1870414772191E-2</v>
+        <v>4.30068945821096E-2</v>
       </c>
       <c r="D31">
-        <v>7.5508739783541889E-2</v>
+        <v>7.5809991886211181E-2</v>
       </c>
       <c r="E31">
-        <v>6.307897039732635E-2</v>
+        <v>6.3882856623741269E-2</v>
       </c>
       <c r="F31">
-        <v>9.5537242826117086E-2</v>
+        <v>9.4923567741025505E-2</v>
       </c>
       <c r="G31">
-        <v>8.8452544528518917E-2</v>
+        <v>8.7801225867549904E-2</v>
       </c>
       <c r="H31">
-        <v>0.1066720260790079</v>
+        <v>0.10397452827060349</v>
       </c>
       <c r="I31">
-        <v>0.12676458159317619</v>
+        <v>0.12562838443853319</v>
       </c>
       <c r="J31">
-        <v>0.15202293147538029</v>
+        <v>0.15164250675461971</v>
       </c>
       <c r="K31">
-        <v>0.17165273725309571</v>
+        <v>0.1713053824921951</v>
       </c>
       <c r="L31">
-        <v>0.18207529231073319</v>
+        <v>0.18269598606998541</v>
       </c>
       <c r="M31">
-        <v>0.1940187754375047</v>
+        <v>0.1920659688399641</v>
       </c>
       <c r="N31">
-        <v>0.22185680391103341</v>
+        <v>0.21643519542252829</v>
       </c>
       <c r="O31">
-        <v>0.26269089990146338</v>
+        <v>0.25793410054427868</v>
       </c>
       <c r="P31">
-        <v>0.26191732529690398</v>
+        <v>0.25661879314238162</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
@@ -2182,49 +2150,49 @@
         <v>46</v>
       </c>
       <c r="B32">
-        <v>2.3968978523144498E-2</v>
+        <v>2.4723769785070741E-2</v>
       </c>
       <c r="C32">
-        <v>4.2497532050364217E-2</v>
+        <v>4.3957323922983238E-2</v>
       </c>
       <c r="D32">
-        <v>6.1776596690832908E-2</v>
+        <v>6.1947228248644959E-2</v>
       </c>
       <c r="E32">
-        <v>6.1010293591956311E-2</v>
+        <v>6.0385788693393512E-2</v>
       </c>
       <c r="F32">
-        <v>9.112419771632474E-2</v>
+        <v>9.2090638588247731E-2</v>
       </c>
       <c r="G32">
-        <v>8.4609955970548434E-2</v>
+        <v>8.5645763039838063E-2</v>
       </c>
       <c r="H32">
-        <v>9.3886314056119691E-2</v>
+        <v>9.3269791841922078E-2</v>
       </c>
       <c r="I32">
-        <v>0.14603534425917061</v>
+        <v>0.14921764244128291</v>
       </c>
       <c r="J32">
-        <v>0.12556205439208151</v>
+        <v>0.12964232790074959</v>
       </c>
       <c r="K32">
-        <v>0.12611337000416831</v>
+        <v>0.13086278420122049</v>
       </c>
       <c r="L32">
-        <v>0.12674597747751951</v>
+        <v>0.13304610795988281</v>
       </c>
       <c r="M32">
-        <v>0.14079857464916459</v>
+        <v>0.14747916404728451</v>
       </c>
       <c r="N32">
-        <v>0.16254079204033409</v>
+        <v>0.17080642454989939</v>
       </c>
       <c r="O32">
-        <v>0.18387109610979971</v>
+        <v>0.1931355189071832</v>
       </c>
       <c r="P32">
-        <v>0.2345238475039674</v>
+        <v>0.24638626378808451</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
@@ -2232,49 +2200,49 @@
         <v>47</v>
       </c>
       <c r="B33">
-        <v>2.6437578736155379E-2</v>
+        <v>2.4160351851025719E-2</v>
       </c>
       <c r="C33">
-        <v>4.5716214619157647E-2</v>
+        <v>4.3462861429619297E-2</v>
       </c>
       <c r="D33">
-        <v>6.2521416793683948E-2</v>
+        <v>6.0366829026244677E-2</v>
       </c>
       <c r="E33">
-        <v>6.1628290518620621E-2</v>
+        <v>5.9813314666671058E-2</v>
       </c>
       <c r="F33">
-        <v>8.8803786554624287E-2</v>
+        <v>9.0127169882396552E-2</v>
       </c>
       <c r="G33">
-        <v>8.2533754245301627E-2</v>
+        <v>8.4758375061715463E-2</v>
       </c>
       <c r="H33">
-        <v>8.9244957664654456E-2</v>
+        <v>9.236584938682646E-2</v>
       </c>
       <c r="I33">
-        <v>0.14196319115741421</v>
+        <v>0.14777249211835791</v>
       </c>
       <c r="J33">
-        <v>0.1222529445698162</v>
+        <v>0.1215913034174968</v>
       </c>
       <c r="K33">
-        <v>0.12404274567295839</v>
+        <v>0.12671148779433969</v>
       </c>
       <c r="L33">
-        <v>0.12516271269620621</v>
+        <v>0.1246600199894117</v>
       </c>
       <c r="M33">
-        <v>0.1391329282717321</v>
+        <v>0.14096108871966281</v>
       </c>
       <c r="N33">
-        <v>0.1601424962856797</v>
+        <v>0.16230456897203679</v>
       </c>
       <c r="O33">
-        <v>0.18360957354154681</v>
+        <v>0.18599558812189429</v>
       </c>
       <c r="P33">
-        <v>0.24024565090160191</v>
+        <v>0.2380015867308555</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
@@ -2282,49 +2250,49 @@
         <v>48</v>
       </c>
       <c r="B34">
-        <v>2.428934059140642E-2</v>
+        <v>2.4562519756207931E-2</v>
       </c>
       <c r="C34">
-        <v>4.31108478309008E-2</v>
+        <v>4.3745961466054473E-2</v>
       </c>
       <c r="D34">
-        <v>6.0540469899884042E-2</v>
+        <v>6.075021552433868E-2</v>
       </c>
       <c r="E34">
-        <v>5.9696032238433672E-2</v>
+        <v>5.9978138524392821E-2</v>
       </c>
       <c r="F34">
-        <v>8.9313716392413589E-2</v>
+        <v>9.0143571931937561E-2</v>
       </c>
       <c r="G34">
-        <v>8.3428703340732269E-2</v>
+        <v>8.1553319455166307E-2</v>
       </c>
       <c r="H34">
-        <v>9.1940077626053274E-2</v>
+        <v>9.0399210085953308E-2</v>
       </c>
       <c r="I34">
-        <v>0.14961687903491649</v>
+        <v>0.14566824546289101</v>
       </c>
       <c r="J34">
-        <v>0.1248858395460242</v>
+        <v>0.12559009622334361</v>
       </c>
       <c r="K34">
-        <v>0.1273057898189314</v>
+        <v>0.1247381261630007</v>
       </c>
       <c r="L34">
-        <v>0.12272965079188609</v>
+        <v>0.1201014150438299</v>
       </c>
       <c r="M34">
-        <v>0.13823249684963279</v>
+        <v>0.1354623558632537</v>
       </c>
       <c r="N34">
-        <v>0.15928293199106561</v>
+        <v>0.15929412911788751</v>
       </c>
       <c r="O34">
-        <v>0.17646564222399841</v>
+        <v>0.17673281569641711</v>
       </c>
       <c r="P34">
-        <v>0.22733195026406161</v>
+        <v>0.23012561104156831</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
@@ -2332,49 +2300,49 @@
         <v>49</v>
       </c>
       <c r="B35">
-        <v>2.5809115735330401E-2</v>
+        <v>2.4428611326919539E-2</v>
       </c>
       <c r="C35">
-        <v>4.4535962217612253E-2</v>
+        <v>4.3675365211720329E-2</v>
       </c>
       <c r="D35">
-        <v>6.2023610713831112E-2</v>
+        <v>6.1603478971335779E-2</v>
       </c>
       <c r="E35">
-        <v>5.9720305028676979E-2</v>
+        <v>5.9590480955062593E-2</v>
       </c>
       <c r="F35">
-        <v>8.773608130320576E-2</v>
+        <v>8.7944437464977487E-2</v>
       </c>
       <c r="G35">
-        <v>8.2221500651674329E-2</v>
+        <v>8.1307021278267499E-2</v>
       </c>
       <c r="H35">
-        <v>9.1218215122695123E-2</v>
+        <v>8.9809966277786701E-2</v>
       </c>
       <c r="I35">
-        <v>0.14666262589946921</v>
+        <v>0.14558733076153019</v>
       </c>
       <c r="J35">
-        <v>0.1240263705721755</v>
+        <v>0.1232481534921297</v>
       </c>
       <c r="K35">
-        <v>0.1301419860246579</v>
+        <v>0.1296282325764602</v>
       </c>
       <c r="L35">
-        <v>0.1194847246667755</v>
+        <v>0.120836308512142</v>
       </c>
       <c r="M35">
-        <v>0.1346041700546563</v>
+        <v>0.1346208028090555</v>
       </c>
       <c r="N35">
-        <v>0.15427699991423949</v>
+        <v>0.15538235547845461</v>
       </c>
       <c r="O35">
-        <v>0.1659508585013604</v>
+        <v>0.17317698498889</v>
       </c>
       <c r="P35">
-        <v>0.21424817630162121</v>
+        <v>0.22495737650526129</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
@@ -2382,49 +2350,49 @@
         <v>50</v>
       </c>
       <c r="B36">
-        <v>2.4449418408932111E-2</v>
+        <v>2.5062006559130271E-2</v>
       </c>
       <c r="C36">
-        <v>4.3246660470288127E-2</v>
+        <v>4.2916740027126088E-2</v>
       </c>
       <c r="D36">
-        <v>5.9829062727698612E-2</v>
+        <v>6.1013945618519923E-2</v>
       </c>
       <c r="E36">
-        <v>5.9129285443393353E-2</v>
+        <v>6.0146968288713687E-2</v>
       </c>
       <c r="F36">
-        <v>9.0352342518632112E-2</v>
+        <v>8.8123298108919834E-2</v>
       </c>
       <c r="G36">
-        <v>8.1973170694652486E-2</v>
+        <v>8.191790864295434E-2</v>
       </c>
       <c r="H36">
-        <v>9.4131418307736414E-2</v>
+        <v>9.1391577679855618E-2</v>
       </c>
       <c r="I36">
-        <v>0.1456441821987223</v>
+        <v>0.14112833252511059</v>
       </c>
       <c r="J36">
-        <v>0.12593033473286511</v>
+        <v>0.1222702788384824</v>
       </c>
       <c r="K36">
-        <v>0.1298234722022733</v>
+        <v>0.12868007384983821</v>
       </c>
       <c r="L36">
-        <v>0.13905165486955501</v>
+        <v>0.13797536971058519</v>
       </c>
       <c r="M36">
-        <v>0.1592965018480037</v>
+        <v>0.15517176698472809</v>
       </c>
       <c r="N36">
-        <v>0.1829566711988708</v>
+        <v>0.18314423980216099</v>
       </c>
       <c r="O36">
-        <v>0.20353239023812869</v>
+        <v>0.20145509892535951</v>
       </c>
       <c r="P36">
-        <v>0.2499493458345633</v>
+        <v>0.2487927252278764</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
@@ -2432,49 +2400,49 @@
         <v>51</v>
       </c>
       <c r="B37">
-        <v>2.7838428763050541E-2</v>
+        <v>2.603196982989919E-2</v>
       </c>
       <c r="C37">
-        <v>4.5774020267515758E-2</v>
+        <v>4.4970418171162208E-2</v>
       </c>
       <c r="D37">
-        <v>6.3511243094212078E-2</v>
+        <v>6.072294965295344E-2</v>
       </c>
       <c r="E37">
-        <v>6.1999305585596187E-2</v>
+        <v>5.9367599933660482E-2</v>
       </c>
       <c r="F37">
-        <v>9.3125516626807348E-2</v>
+        <v>8.9579637428362058E-2</v>
       </c>
       <c r="G37">
-        <v>8.7296495103012961E-2</v>
+        <v>8.2818941730974371E-2</v>
       </c>
       <c r="H37">
-        <v>9.669753992591934E-2</v>
+        <v>9.0287391705176745E-2</v>
       </c>
       <c r="I37">
-        <v>0.14704776382921711</v>
+        <v>0.14510825725645229</v>
       </c>
       <c r="J37">
-        <v>0.1263888628145492</v>
+        <v>0.1245962082251295</v>
       </c>
       <c r="K37">
-        <v>0.13379990175645429</v>
+        <v>0.13077819452979661</v>
       </c>
       <c r="L37">
-        <v>0.1387851996643901</v>
+        <v>0.13702109075040839</v>
       </c>
       <c r="M37">
-        <v>0.15641688963396541</v>
+        <v>0.1554104600533377</v>
       </c>
       <c r="N37">
-        <v>0.1781908507658477</v>
+        <v>0.18216397736493131</v>
       </c>
       <c r="O37">
-        <v>0.1983131069416314</v>
+        <v>0.20508714524753929</v>
       </c>
       <c r="P37">
-        <v>0.24941899397351949</v>
+        <v>0.25400716406064061</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
@@ -2482,49 +2450,49 @@
         <v>52</v>
       </c>
       <c r="B38">
-        <v>2.4742995870510761E-2</v>
+        <v>2.459263824912605E-2</v>
       </c>
       <c r="C38">
-        <v>4.3597066435588472E-2</v>
+        <v>4.2777044811612368E-2</v>
       </c>
       <c r="D38">
-        <v>6.0408165094754107E-2</v>
+        <v>6.0740001131238557E-2</v>
       </c>
       <c r="E38">
-        <v>5.8958624944172588E-2</v>
+        <v>5.9465628946525302E-2</v>
       </c>
       <c r="F38">
-        <v>8.8485023600353818E-2</v>
+        <v>9.0740913881234175E-2</v>
       </c>
       <c r="G38">
-        <v>8.0718433710637361E-2</v>
+        <v>8.3668683220170736E-2</v>
       </c>
       <c r="H38">
-        <v>9.2101733040617306E-2</v>
+        <v>9.2825043142131691E-2</v>
       </c>
       <c r="I38">
-        <v>0.1395840432396914</v>
+        <v>0.1423725602251725</v>
       </c>
       <c r="J38">
-        <v>0.12264056438184109</v>
+        <v>0.12355855319050291</v>
       </c>
       <c r="K38">
-        <v>0.12325448483571599</v>
+        <v>0.12846751938449791</v>
       </c>
       <c r="L38">
-        <v>0.1324837444364356</v>
+        <v>0.13433906719342811</v>
       </c>
       <c r="M38">
-        <v>0.1459880854095468</v>
+        <v>0.14802910296179081</v>
       </c>
       <c r="N38">
-        <v>0.16826547967582139</v>
+        <v>0.17150860971788681</v>
       </c>
       <c r="O38">
-        <v>0.19046260304533619</v>
+        <v>0.19103679194833451</v>
       </c>
       <c r="P38">
-        <v>0.2449912904229502</v>
+        <v>0.25329738002399499</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
@@ -2532,49 +2500,49 @@
         <v>53</v>
       </c>
       <c r="B39">
-        <v>2.5794974930058889E-2</v>
+        <v>2.3985964471841651E-2</v>
       </c>
       <c r="C39">
-        <v>4.5237344501723793E-2</v>
+        <v>4.3309932660338002E-2</v>
       </c>
       <c r="D39">
-        <v>6.3865013869330522E-2</v>
+        <v>5.9193098122343628E-2</v>
       </c>
       <c r="E39">
-        <v>6.0936221711682781E-2</v>
+        <v>5.8101167509179263E-2</v>
       </c>
       <c r="F39">
-        <v>9.1817694870495292E-2</v>
+        <v>8.8290601770394384E-2</v>
       </c>
       <c r="G39">
-        <v>8.5804355511970298E-2</v>
+        <v>8.0301260148129439E-2</v>
       </c>
       <c r="H39">
-        <v>9.4104890190626289E-2</v>
+        <v>9.2277603079697124E-2</v>
       </c>
       <c r="I39">
-        <v>0.14772212829185549</v>
+        <v>0.144666228384011</v>
       </c>
       <c r="J39">
-        <v>0.12724658688424809</v>
+        <v>0.1228316707019949</v>
       </c>
       <c r="K39">
-        <v>0.12798227638680601</v>
+        <v>0.12688543017727719</v>
       </c>
       <c r="L39">
-        <v>0.13300860486055871</v>
+        <v>0.13265268008561429</v>
       </c>
       <c r="M39">
-        <v>0.1476989319414006</v>
+        <v>0.1480550085757307</v>
       </c>
       <c r="N39">
-        <v>0.16991852547306141</v>
+        <v>0.16718999282932259</v>
       </c>
       <c r="O39">
-        <v>0.18519480085041179</v>
+        <v>0.1909276178765513</v>
       </c>
       <c r="P39">
-        <v>0.23953169383214021</v>
+        <v>0.24830837509371301</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
@@ -2582,49 +2550,49 @@
         <v>54</v>
       </c>
       <c r="B40">
-        <v>2.5805145933734289E-2</v>
+        <v>2.367106427108789E-2</v>
       </c>
       <c r="C40">
-        <v>4.3721185667678353E-2</v>
+        <v>4.3357192647390352E-2</v>
       </c>
       <c r="D40">
-        <v>5.9958694602699647E-2</v>
+        <v>6.2294623284278712E-2</v>
       </c>
       <c r="E40">
-        <v>5.8575302841746613E-2</v>
+        <v>6.0894923275267472E-2</v>
       </c>
       <c r="F40">
-        <v>8.6266825166952832E-2</v>
+        <v>9.0973268377082972E-2</v>
       </c>
       <c r="G40">
-        <v>8.068220896190248E-2</v>
+        <v>8.5037899088389213E-2</v>
       </c>
       <c r="H40">
-        <v>9.0143342466567855E-2</v>
+        <v>9.4043545818516039E-2</v>
       </c>
       <c r="I40">
-        <v>0.1414444342019581</v>
+        <v>0.1503291154307986</v>
       </c>
       <c r="J40">
-        <v>0.1202129417037081</v>
+        <v>0.12656988331146879</v>
       </c>
       <c r="K40">
-        <v>0.12986845091872509</v>
+        <v>0.13321900533052181</v>
       </c>
       <c r="L40">
-        <v>0.1208092541308472</v>
+        <v>0.12329617185782191</v>
       </c>
       <c r="M40">
-        <v>0.1353364721960113</v>
+        <v>0.13836937382391809</v>
       </c>
       <c r="N40">
-        <v>0.15502180406261259</v>
+        <v>0.15774317941723229</v>
       </c>
       <c r="O40">
-        <v>0.16828358114291789</v>
+        <v>0.16920336584645931</v>
       </c>
       <c r="P40">
-        <v>0.22613420854762031</v>
+        <v>0.22469639272824249</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
@@ -2632,49 +2600,49 @@
         <v>55</v>
       </c>
       <c r="B41">
-        <v>2.5222618236111272E-2</v>
+        <v>2.5390968813600919E-2</v>
       </c>
       <c r="C41">
-        <v>0.12289180791749189</v>
+        <v>0.1194115580096166</v>
       </c>
       <c r="D41">
-        <v>7.9044105718657498E-2</v>
+        <v>7.5124591080072634E-2</v>
       </c>
       <c r="E41">
-        <v>9.2318186807080149E-2</v>
+        <v>8.8086035526678708E-2</v>
       </c>
       <c r="F41">
-        <v>0.1395833010460138</v>
+        <v>0.13393981452795509</v>
       </c>
       <c r="G41">
-        <v>0.23583865043835739</v>
+        <v>0.22567163669438459</v>
       </c>
       <c r="H41">
-        <v>0.25904767968397291</v>
+        <v>0.2468855759544584</v>
       </c>
       <c r="I41">
-        <v>0.29109969922206491</v>
+        <v>0.28188786768343688</v>
       </c>
       <c r="J41">
-        <v>0.32291760435280492</v>
+        <v>0.31317076648740028</v>
       </c>
       <c r="K41">
-        <v>0.33060946679841452</v>
+        <v>0.3239335147847372</v>
       </c>
       <c r="L41">
-        <v>0.3729472456041999</v>
+        <v>0.36261442965624979</v>
       </c>
       <c r="M41">
-        <v>0.38322796522947228</v>
+        <v>0.37449475585635089</v>
       </c>
       <c r="N41">
-        <v>0.40815448856925879</v>
+        <v>0.39874147922088948</v>
       </c>
       <c r="O41">
-        <v>0.43145899421255218</v>
+        <v>0.4234474486974763</v>
       </c>
       <c r="P41">
-        <v>0.4458653043198611</v>
+        <v>0.44045552637795032</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
@@ -2682,49 +2650,49 @@
         <v>56</v>
       </c>
       <c r="B42">
-        <v>2.4523157413091971E-2</v>
+        <v>2.474988438987091E-2</v>
       </c>
       <c r="C42">
-        <v>0.10716607778959621</v>
+        <v>0.112677674330515</v>
       </c>
       <c r="D42">
-        <v>5.7083706908762522E-2</v>
+        <v>6.1268325752683588E-2</v>
       </c>
       <c r="E42">
-        <v>7.0392859947930542E-2</v>
+        <v>7.5940424419506658E-2</v>
       </c>
       <c r="F42">
-        <v>0.1175227139870222</v>
+        <v>0.1219945364638949</v>
       </c>
       <c r="G42">
-        <v>0.18797792497156951</v>
+        <v>0.19429460915187871</v>
       </c>
       <c r="H42">
-        <v>0.2018531489964612</v>
+        <v>0.20252517751782381</v>
       </c>
       <c r="I42">
-        <v>0.21693157807673941</v>
+        <v>0.22026339047817339</v>
       </c>
       <c r="J42">
-        <v>0.21917355184097501</v>
+        <v>0.22103584019133329</v>
       </c>
       <c r="K42">
-        <v>0.21801009149819309</v>
+        <v>0.21598549106752399</v>
       </c>
       <c r="L42">
-        <v>0.23047283712004449</v>
+        <v>0.2311703268124469</v>
       </c>
       <c r="M42">
-        <v>0.25232534670058338</v>
+        <v>0.25108251223559491</v>
       </c>
       <c r="N42">
-        <v>0.26190410421032151</v>
+        <v>0.2590784989240501</v>
       </c>
       <c r="O42">
-        <v>0.28985974316896479</v>
+        <v>0.2853638637691932</v>
       </c>
       <c r="P42">
-        <v>0.33481814459536502</v>
+        <v>0.33198248813713638</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
@@ -2732,49 +2700,49 @@
         <v>57</v>
       </c>
       <c r="B43">
-        <v>2.358931281877685E-2</v>
+        <v>2.5963540494163939E-2</v>
       </c>
       <c r="C43">
-        <v>0.1095409111934659</v>
+        <v>0.1143007045334147</v>
       </c>
       <c r="D43">
-        <v>5.6988568437615239E-2</v>
+        <v>6.1185332922271463E-2</v>
       </c>
       <c r="E43">
-        <v>7.1397250851294891E-2</v>
+        <v>7.5916714441661037E-2</v>
       </c>
       <c r="F43">
-        <v>0.12713162934584371</v>
+        <v>0.12935643841403119</v>
       </c>
       <c r="G43">
-        <v>0.1794274460518718</v>
+        <v>0.1874834826425551</v>
       </c>
       <c r="H43">
-        <v>0.1762386573124799</v>
+        <v>0.18267383573738841</v>
       </c>
       <c r="I43">
-        <v>0.1935977389858963</v>
+        <v>0.20175018280778181</v>
       </c>
       <c r="J43">
-        <v>0.19654811799167249</v>
+        <v>0.2038519814411193</v>
       </c>
       <c r="K43">
-        <v>0.19934746236132339</v>
+        <v>0.20419024742942729</v>
       </c>
       <c r="L43">
-        <v>0.21909054841433481</v>
+        <v>0.22140725438853201</v>
       </c>
       <c r="M43">
-        <v>0.23928109318500049</v>
+        <v>0.24390849623401609</v>
       </c>
       <c r="N43">
-        <v>0.24300775433981761</v>
+        <v>0.24738982267244769</v>
       </c>
       <c r="O43">
-        <v>0.25870162074121911</v>
+        <v>0.26162000857662582</v>
       </c>
       <c r="P43">
-        <v>0.29984737528033661</v>
+        <v>0.30502710143214617</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
@@ -2782,49 +2750,49 @@
         <v>58</v>
       </c>
       <c r="B44">
-        <v>3.1515613424670803E-2</v>
+        <v>3.0988070394335491E-2</v>
       </c>
       <c r="C44">
-        <v>9.0117888140391345E-2</v>
+        <v>9.0525787226068966E-2</v>
       </c>
       <c r="D44">
-        <v>0.11092684462997759</v>
+        <v>0.11134330849386539</v>
       </c>
       <c r="E44">
-        <v>7.2712018313841997E-2</v>
+        <v>7.0284598014564548E-2</v>
       </c>
       <c r="F44">
-        <v>0.13202915011736349</v>
+        <v>0.1261405110554541</v>
       </c>
       <c r="G44">
-        <v>0.16342518173868401</v>
+        <v>0.15581267938134311</v>
       </c>
       <c r="H44">
-        <v>0.20345420369722861</v>
+        <v>0.1982106752992836</v>
       </c>
       <c r="I44">
-        <v>0.22509181942129861</v>
+        <v>0.2184809520107476</v>
       </c>
       <c r="J44">
-        <v>0.25270274505276819</v>
+        <v>0.24728910426391909</v>
       </c>
       <c r="K44">
-        <v>0.30331348452216461</v>
+        <v>0.29849189631538731</v>
       </c>
       <c r="L44">
-        <v>0.35575586016529759</v>
+        <v>0.3508380105691925</v>
       </c>
       <c r="M44">
-        <v>0.39661105824025611</v>
+        <v>0.39104744037691852</v>
       </c>
       <c r="N44">
-        <v>0.43424115171412969</v>
+        <v>0.42940635013282658</v>
       </c>
       <c r="O44">
-        <v>0.47118478339489572</v>
+        <v>0.46641038420682063</v>
       </c>
       <c r="P44">
-        <v>0.53048719009329193</v>
+        <v>0.52814793276832761</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
@@ -2832,49 +2800,49 @@
         <v>59</v>
       </c>
       <c r="B45">
-        <v>4.1550285331456549E-2</v>
+        <v>4.0046141662883339E-2</v>
       </c>
       <c r="C45">
-        <v>6.4343568526558981E-2</v>
+        <v>6.4265165893398479E-2</v>
       </c>
       <c r="D45">
-        <v>0.13291972940619631</v>
+        <v>0.13246336208018719</v>
       </c>
       <c r="E45">
-        <v>0.20239917635099419</v>
+        <v>0.2018495102669324</v>
       </c>
       <c r="F45">
-        <v>0.29983130426528559</v>
+        <v>0.2956611313275701</v>
       </c>
       <c r="G45">
-        <v>0.36782656518764628</v>
+        <v>0.35444510564309872</v>
       </c>
       <c r="H45">
-        <v>0.37554148824232753</v>
+        <v>0.3628997647706631</v>
       </c>
       <c r="I45">
-        <v>0.38573481973176632</v>
+        <v>0.37897476082936787</v>
       </c>
       <c r="J45">
-        <v>0.41601687723705238</v>
+        <v>0.40936707991830129</v>
       </c>
       <c r="K45">
-        <v>0.51937041742530687</v>
+        <v>0.51154300743051184</v>
       </c>
       <c r="L45">
-        <v>0.58764371163479967</v>
+        <v>0.58560801273952734</v>
       </c>
       <c r="M45">
-        <v>0.63106667138768768</v>
+        <v>0.63081197820879942</v>
       </c>
       <c r="N45">
-        <v>0.70135279461687661</v>
+        <v>0.70585086948846465</v>
       </c>
       <c r="O45">
-        <v>0.74240905931668744</v>
+        <v>0.74908140116666067</v>
       </c>
       <c r="P45">
-        <v>0.72694547490122918</v>
+        <v>0.73692877775671062</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
@@ -2882,49 +2850,49 @@
         <v>60</v>
       </c>
       <c r="B46">
-        <v>4.7838926479357613E-2</v>
+        <v>4.6777482586753523E-2</v>
       </c>
       <c r="C46">
-        <v>4.7343488542324293E-2</v>
+        <v>4.6260938638123313E-2</v>
       </c>
       <c r="D46">
-        <v>0.11177109253150221</v>
+        <v>0.1042264529030448</v>
       </c>
       <c r="E46">
-        <v>0.16561977487281609</v>
+        <v>0.16201054752210339</v>
       </c>
       <c r="F46">
-        <v>0.25999169936922423</v>
+        <v>0.24954866208469129</v>
       </c>
       <c r="G46">
-        <v>0.25515494515847092</v>
+        <v>0.24702660583109129</v>
       </c>
       <c r="H46">
-        <v>0.28871282370610279</v>
+        <v>0.28254282059237751</v>
       </c>
       <c r="I46">
-        <v>0.3601851440304375</v>
+        <v>0.34851079798926371</v>
       </c>
       <c r="J46">
-        <v>0.4596900817852555</v>
+        <v>0.44265018017266389</v>
       </c>
       <c r="K46">
-        <v>0.56973555764829786</v>
+        <v>0.54977677825621263</v>
       </c>
       <c r="L46">
-        <v>0.60837890337117551</v>
+        <v>0.5940487585320855</v>
       </c>
       <c r="M46">
-        <v>0.65402414389164365</v>
+        <v>0.6370679258050439</v>
       </c>
       <c r="N46">
-        <v>0.69103123234492037</v>
+        <v>0.67255025977287808</v>
       </c>
       <c r="O46">
-        <v>0.71378987290554585</v>
+        <v>0.69587444675024379</v>
       </c>
       <c r="P46">
-        <v>0.7203326827600578</v>
+        <v>0.69936524815328538</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
@@ -2932,61 +2900,60 @@
         <v>61</v>
       </c>
       <c r="B47">
-        <v>3.054557286706094E-2</v>
+        <v>3.341212425483675E-2</v>
       </c>
       <c r="C47">
-        <v>9.0392380509241921E-2</v>
+        <v>9.5965316816099322E-2</v>
       </c>
       <c r="D47">
-        <v>0.13214304622603851</v>
+        <v>0.14154945853889761</v>
       </c>
       <c r="E47">
-        <v>0.1922509025393217</v>
+        <v>0.20504528536010111</v>
       </c>
       <c r="F47">
-        <v>0.33780105537691318</v>
+        <v>0.34988525713856677</v>
       </c>
       <c r="G47">
-        <v>0.33169650368840198</v>
+        <v>0.34813655380133768</v>
       </c>
       <c r="H47">
-        <v>0.33302996227172599</v>
+        <v>0.3390595290928769</v>
       </c>
       <c r="I47">
-        <v>0.3421450702692051</v>
+        <v>0.35526770948806669</v>
       </c>
       <c r="J47">
-        <v>0.4336849204247411</v>
+        <v>0.45015267980469098</v>
       </c>
       <c r="K47">
-        <v>0.4497915175352824</v>
+        <v>0.46888383434621778</v>
       </c>
       <c r="L47">
-        <v>0.5072501851834863</v>
+        <v>0.52778122368904912</v>
       </c>
       <c r="M47">
-        <v>0.53943519756412228</v>
+        <v>0.56191762255768096</v>
       </c>
       <c r="N47">
-        <v>0.54507771955503648</v>
+        <v>0.56277863304306219</v>
       </c>
       <c r="O47">
-        <v>0.55625135545913107</v>
+        <v>0.57286187657253107</v>
       </c>
       <c r="P47">
-        <v>0.56869299903075521</v>
+        <v>0.58450260341115023</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:P28 B30:P47 B29:I29 K29:P29">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="lessThan">
+  <conditionalFormatting sqref="B2:P47">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
       <formula>0.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>0.2</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ROSA_vitaSPEC/Results/test_pretraitements/total.trans.carotenes.natif/Resultats_total.trans.carotenes.natif_moy_diff.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/total.trans.carotenes.natif/Resultats_total.trans.carotenes.natif_moy_diff.xlsx
@@ -1,217 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\total.trans.carotenes.natif\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
-  <si>
-    <t>Pretraitement</t>
-  </si>
-  <si>
-    <t>LV1_diff</t>
-  </si>
-  <si>
-    <t>LV2_diff</t>
-  </si>
-  <si>
-    <t>LV3_diff</t>
-  </si>
-  <si>
-    <t>LV4_diff</t>
-  </si>
-  <si>
-    <t>LV5_diff</t>
-  </si>
-  <si>
-    <t>LV6_diff</t>
-  </si>
-  <si>
-    <t>LV7_diff</t>
-  </si>
-  <si>
-    <t>LV8_diff</t>
-  </si>
-  <si>
-    <t>LV9_diff</t>
-  </si>
-  <si>
-    <t>LV10_diff</t>
-  </si>
-  <si>
-    <t>LV11_diff</t>
-  </si>
-  <si>
-    <t>LV12_diff</t>
-  </si>
-  <si>
-    <t>LV13_diff</t>
-  </si>
-  <si>
-    <t>LV14_diff</t>
-  </si>
-  <si>
-    <t>LV15_diff</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1000,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(1,3,5)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -257,52 +61,13 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -344,7 +109,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -376,10 +141,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -411,7 +175,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -587,2373 +350,2277 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="16" width="12" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P43"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>16</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pretraitement</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>LV1_diff</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LV2_diff</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LV3_diff</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>LV4_diff</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>LV5_diff</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LV6_diff</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LV7_diff</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LV8_diff</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LV9_diff</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>LV10_diff</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>LV11_diff</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>LV12_diff</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>LV13_diff</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>LV14_diff</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>LV15_diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1000,1)_snv_</t>
+        </is>
       </c>
       <c r="B2">
-        <v>3.8915285292921757E-2</v>
+        <v>0.03625045240277963</v>
       </c>
       <c r="C2">
-        <v>6.7013611274047813E-2</v>
+        <v>0.06431666471479336</v>
       </c>
       <c r="D2">
-        <v>9.0767685146846855E-2</v>
+        <v>0.08873194326611877</v>
       </c>
       <c r="E2">
-        <v>8.5596280374460432E-2</v>
+        <v>0.08417881016784001</v>
       </c>
       <c r="F2">
-        <v>0.1319659088989544</v>
+        <v>0.1285134205583662</v>
       </c>
       <c r="G2">
-        <v>0.1276891677471019</v>
+        <v>0.1231192799431258</v>
       </c>
       <c r="H2">
-        <v>0.12952066162752679</v>
+        <v>0.1254373496448788</v>
       </c>
       <c r="I2">
-        <v>0.14466490960115461</v>
+        <v>0.1403276732924035</v>
       </c>
       <c r="J2">
-        <v>0.18701711596600751</v>
+        <v>0.1818606389782489</v>
       </c>
       <c r="K2">
-        <v>0.2353128907291476</v>
+        <v>0.2306937721056249</v>
       </c>
       <c r="L2">
-        <v>0.24116982832047729</v>
+        <v>0.2403918460991417</v>
       </c>
       <c r="M2">
-        <v>0.30002229171739708</v>
+        <v>0.2960730579652044</v>
       </c>
       <c r="N2">
-        <v>0.35212148822887629</v>
+        <v>0.348666267882334</v>
       </c>
       <c r="O2">
-        <v>0.37937042812957988</v>
+        <v>0.372015293007984</v>
       </c>
       <c r="P2">
-        <v>0.37722402340742422</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>17</v>
+        <v>0.3710497707384472</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B3">
-        <v>4.1947943674877357E-2</v>
+        <v>0.04479994777326762</v>
       </c>
       <c r="C3">
-        <v>4.0141782472616017E-2</v>
+        <v>0.04402598458562623</v>
       </c>
       <c r="D3">
-        <v>7.6349113095919519E-2</v>
+        <v>0.0816088811691088</v>
       </c>
       <c r="E3">
-        <v>0.1071599275775539</v>
+        <v>0.1121354635843348</v>
       </c>
       <c r="F3">
-        <v>0.16463767525544151</v>
+        <v>0.1680304527884569</v>
       </c>
       <c r="G3">
-        <v>0.20332063049081719</v>
+        <v>0.2074718037455313</v>
       </c>
       <c r="H3">
-        <v>0.28870730880481588</v>
+        <v>0.2889679158503772</v>
       </c>
       <c r="I3">
-        <v>0.32641898378987072</v>
+        <v>0.3260497902428575</v>
       </c>
       <c r="J3">
-        <v>0.36235177950524428</v>
+        <v>0.3617038175094479</v>
       </c>
       <c r="K3">
-        <v>0.37103711628550329</v>
+        <v>0.367540373479749</v>
       </c>
       <c r="L3">
-        <v>0.41055975959907642</v>
+        <v>0.4076622430592141</v>
       </c>
       <c r="M3">
-        <v>0.49354193039229072</v>
+        <v>0.4899676140122085</v>
       </c>
       <c r="N3">
-        <v>0.58036622171148111</v>
+        <v>0.5730522611830919</v>
       </c>
       <c r="O3">
-        <v>0.65080072725065563</v>
+        <v>0.6419535806388363</v>
       </c>
       <c r="P3">
-        <v>0.72041323687534753</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>18</v>
+        <v>0.7058070413938077</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B4">
-        <v>3.3835160913421418E-2</v>
+        <v>0.03400180739534092</v>
       </c>
       <c r="C4">
-        <v>5.7347226095890602E-2</v>
+        <v>0.05740003275338706</v>
       </c>
       <c r="D4">
-        <v>7.1955365095613844E-2</v>
+        <v>0.07218280441630798</v>
       </c>
       <c r="E4">
-        <v>0.1210045405201913</v>
+        <v>0.1248663188227252</v>
       </c>
       <c r="F4">
-        <v>0.1353207649946899</v>
+        <v>0.1388488039490986</v>
       </c>
       <c r="G4">
-        <v>0.14368813654030491</v>
+        <v>0.1478989534226014</v>
       </c>
       <c r="H4">
-        <v>0.13915089479142931</v>
+        <v>0.1371607028663091</v>
       </c>
       <c r="I4">
-        <v>0.17450299509745371</v>
+        <v>0.1748805787992896</v>
       </c>
       <c r="J4">
-        <v>0.2209229710468692</v>
+        <v>0.2194090044919488</v>
       </c>
       <c r="K4">
-        <v>0.32828099271014533</v>
+        <v>0.324735236259459</v>
       </c>
       <c r="L4">
-        <v>0.3740482612367414</v>
+        <v>0.3736836191836407</v>
       </c>
       <c r="M4">
-        <v>0.37721336698789992</v>
+        <v>0.3742391536495331</v>
       </c>
       <c r="N4">
-        <v>0.38511784278724548</v>
+        <v>0.3774672445539454</v>
       </c>
       <c r="O4">
-        <v>0.4095126317084799</v>
+        <v>0.403064915537142</v>
       </c>
       <c r="P4">
-        <v>0.42019086225146179</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>19</v>
+        <v>0.4096522268131046</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B5">
-        <v>2.7997208810666922E-2</v>
+        <v>0.02856815106228305</v>
       </c>
       <c r="C5">
-        <v>5.5953494258544567E-2</v>
+        <v>0.05748903418685625</v>
       </c>
       <c r="D5">
-        <v>9.666350795220402E-2</v>
+        <v>0.09810714618532512</v>
       </c>
       <c r="E5">
-        <v>0.13173385518987021</v>
+        <v>0.1290850252274132</v>
       </c>
       <c r="F5">
-        <v>0.18255611676881039</v>
+        <v>0.1795248385851094</v>
       </c>
       <c r="G5">
-        <v>0.20680134473018191</v>
+        <v>0.2066627070385573</v>
       </c>
       <c r="H5">
-        <v>0.23870663597831299</v>
+        <v>0.2373789351600383</v>
       </c>
       <c r="I5">
-        <v>0.28178619802855598</v>
+        <v>0.276052817054874</v>
       </c>
       <c r="J5">
-        <v>0.34111623965771698</v>
+        <v>0.3286380747626099</v>
       </c>
       <c r="K5">
-        <v>0.36377592529893887</v>
+        <v>0.3489124896332287</v>
       </c>
       <c r="L5">
-        <v>0.40170405732650921</v>
+        <v>0.3870952986078682</v>
       </c>
       <c r="M5">
-        <v>0.42496192412130263</v>
+        <v>0.4176213736585773</v>
       </c>
       <c r="N5">
-        <v>0.45999040467768448</v>
+        <v>0.4506964811633067</v>
       </c>
       <c r="O5">
-        <v>0.50068931960293961</v>
+        <v>0.4895943797632508</v>
       </c>
       <c r="P5">
-        <v>0.49909628960712249</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>20</v>
+        <v>0.4867375059461493</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B6">
-        <v>2.7009047170418961E-2</v>
+        <v>0.02802057943221115</v>
       </c>
       <c r="C6">
-        <v>5.3764413713701553E-2</v>
+        <v>0.05644913947072805</v>
       </c>
       <c r="D6">
-        <v>7.7937895082812791E-2</v>
+        <v>0.08238024090586393</v>
       </c>
       <c r="E6">
-        <v>0.1333553445852492</v>
+        <v>0.1416947079162113</v>
       </c>
       <c r="F6">
-        <v>0.16625524551126589</v>
+        <v>0.1716362604013185</v>
       </c>
       <c r="G6">
-        <v>0.21825475569437311</v>
+        <v>0.2304672342131281</v>
       </c>
       <c r="H6">
-        <v>0.23292299835345051</v>
+        <v>0.2485265308288011</v>
       </c>
       <c r="I6">
-        <v>0.28259168867593631</v>
+        <v>0.2949183324965317</v>
       </c>
       <c r="J6">
-        <v>0.2995841601293</v>
+        <v>0.3111724526475861</v>
       </c>
       <c r="K6">
-        <v>0.32134370431339271</v>
+        <v>0.3355373610415462</v>
       </c>
       <c r="L6">
-        <v>0.37401797481435273</v>
+        <v>0.3885905140068652</v>
       </c>
       <c r="M6">
-        <v>0.44364121746448643</v>
+        <v>0.4590526893553136</v>
       </c>
       <c r="N6">
-        <v>0.50465332639574578</v>
+        <v>0.5206819405393229</v>
       </c>
       <c r="O6">
-        <v>0.52581031544180679</v>
+        <v>0.5401764631603421</v>
       </c>
       <c r="P6">
-        <v>0.50004623973548978</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>21</v>
+        <v>0.5126589403634795</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B7">
-        <v>3.6022600216342571E-2</v>
+        <v>0.03527227668954486</v>
       </c>
       <c r="C7">
-        <v>5.7370290730546232E-2</v>
+        <v>0.05605552037648753</v>
       </c>
       <c r="D7">
-        <v>8.7446815292332114E-2</v>
+        <v>0.08543579270351076</v>
       </c>
       <c r="E7">
-        <v>7.5654245246991714E-2</v>
+        <v>0.07329131303865299</v>
       </c>
       <c r="F7">
-        <v>0.1007763964630323</v>
+        <v>0.09722966295500246</v>
       </c>
       <c r="G7">
-        <v>9.4846690029648406E-2</v>
+        <v>0.09229249976926868</v>
       </c>
       <c r="H7">
-        <v>0.12436520004798519</v>
+        <v>0.1211876001017974</v>
       </c>
       <c r="I7">
-        <v>0.15607602382392771</v>
+        <v>0.1521877447603311</v>
       </c>
       <c r="J7">
-        <v>0.18982921855027701</v>
+        <v>0.1854015460193427</v>
       </c>
       <c r="K7">
-        <v>0.21653535916014441</v>
+        <v>0.2161088329239964</v>
       </c>
       <c r="L7">
-        <v>0.30894855810543292</v>
+        <v>0.3047197830722757</v>
       </c>
       <c r="M7">
-        <v>0.31157862830252819</v>
+        <v>0.3099000635748109</v>
       </c>
       <c r="N7">
-        <v>0.30497198293578542</v>
+        <v>0.2996451952185302</v>
       </c>
       <c r="O7">
-        <v>0.313666997281558</v>
+        <v>0.3095193509049865</v>
       </c>
       <c r="P7">
-        <v>0.32647873461778842</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>22</v>
+        <v>0.3232189985306283</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B8">
-        <v>3.0897142413666919E-2</v>
+        <v>0.03523057921556483</v>
       </c>
       <c r="C8">
-        <v>5.4242656818098138E-2</v>
+        <v>0.05906288296401385</v>
       </c>
       <c r="D8">
-        <v>9.4331657716207551E-2</v>
+        <v>0.09619162533609693</v>
       </c>
       <c r="E8">
-        <v>0.1160299866925675</v>
+        <v>0.1169522810787853</v>
       </c>
       <c r="F8">
-        <v>0.1204660997687093</v>
+        <v>0.1178311623706634</v>
       </c>
       <c r="G8">
-        <v>0.169002726611995</v>
+        <v>0.1687306897679495</v>
       </c>
       <c r="H8">
-        <v>0.18616796856663029</v>
+        <v>0.1859186961719468</v>
       </c>
       <c r="I8">
-        <v>0.2016740095290914</v>
+        <v>0.19920743580184</v>
       </c>
       <c r="J8">
-        <v>0.29167098598810831</v>
+        <v>0.2873947540183414</v>
       </c>
       <c r="K8">
-        <v>0.35554627651278259</v>
+        <v>0.3457746033115149</v>
       </c>
       <c r="L8">
-        <v>0.36771941173088779</v>
+        <v>0.3557260051917738</v>
       </c>
       <c r="M8">
-        <v>0.36163615013531941</v>
+        <v>0.3511740896179505</v>
       </c>
       <c r="N8">
-        <v>0.35348104855410822</v>
+        <v>0.341707639674221</v>
       </c>
       <c r="O8">
-        <v>0.38730211218242189</v>
+        <v>0.377432702986834</v>
       </c>
       <c r="P8">
-        <v>0.39242558042129339</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>23</v>
+        <v>0.3817528594387312</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B9">
-        <v>3.1398802445218137E-2</v>
+        <v>0.03479783887569327</v>
       </c>
       <c r="C9">
-        <v>5.6809214116957329E-2</v>
+        <v>0.05929398075182973</v>
       </c>
       <c r="D9">
-        <v>9.5488525582447914E-2</v>
+        <v>0.09676723042914381</v>
       </c>
       <c r="E9">
-        <v>0.1174690279726488</v>
+        <v>0.1179327570109797</v>
       </c>
       <c r="F9">
-        <v>0.1194560451002902</v>
+        <v>0.1205553469266487</v>
       </c>
       <c r="G9">
-        <v>0.15920252678419619</v>
+        <v>0.162951633606353</v>
       </c>
       <c r="H9">
-        <v>0.17446370263871491</v>
+        <v>0.1787598130823086</v>
       </c>
       <c r="I9">
-        <v>0.1734752962655309</v>
+        <v>0.1731634098974258</v>
       </c>
       <c r="J9">
-        <v>0.2309430433005161</v>
+        <v>0.2319468633754581</v>
       </c>
       <c r="K9">
-        <v>0.28317993354695592</v>
+        <v>0.2874073310505701</v>
       </c>
       <c r="L9">
-        <v>0.31371036468482483</v>
+        <v>0.313192395099717</v>
       </c>
       <c r="M9">
-        <v>0.30325351464789591</v>
+        <v>0.3026719450484774</v>
       </c>
       <c r="N9">
-        <v>0.28230868614668958</v>
+        <v>0.2823217934456662</v>
       </c>
       <c r="O9">
-        <v>0.30054850551968598</v>
+        <v>0.2999375307742355</v>
       </c>
       <c r="P9">
-        <v>0.3267697862338213</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>24</v>
+        <v>0.3254751916514674</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B10">
-        <v>3.07099306947668E-2</v>
+        <v>0.03114008686399661</v>
       </c>
       <c r="C10">
-        <v>5.3967833842007477E-2</v>
+        <v>0.0549304380492141</v>
       </c>
       <c r="D10">
-        <v>8.7889837316044495E-2</v>
+        <v>0.09057263303786034</v>
       </c>
       <c r="E10">
-        <v>0.10824391812876449</v>
+        <v>0.1117136343044263</v>
       </c>
       <c r="F10">
-        <v>0.112808644911878</v>
+        <v>0.1142215589471557</v>
       </c>
       <c r="G10">
-        <v>0.1532318940183035</v>
+        <v>0.155787613447861</v>
       </c>
       <c r="H10">
-        <v>0.1688386859905511</v>
+        <v>0.1731006193529089</v>
       </c>
       <c r="I10">
-        <v>0.16333005807855339</v>
+        <v>0.1683886736993581</v>
       </c>
       <c r="J10">
-        <v>0.2180106467024332</v>
+        <v>0.2276498635475929</v>
       </c>
       <c r="K10">
-        <v>0.2745525029926193</v>
+        <v>0.2871544260821395</v>
       </c>
       <c r="L10">
-        <v>0.3040626598141567</v>
+        <v>0.3160094942821731</v>
       </c>
       <c r="M10">
-        <v>0.29290162908173789</v>
+        <v>0.3040578187494176</v>
       </c>
       <c r="N10">
-        <v>0.2712437879549654</v>
+        <v>0.2785730733093791</v>
       </c>
       <c r="O10">
-        <v>0.28308499100808898</v>
+        <v>0.2902854748598056</v>
       </c>
       <c r="P10">
-        <v>0.30907407504145878</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>25</v>
+        <v>0.3127560248305634</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B11">
-        <v>3.1925983526622959E-2</v>
+        <v>0.03272895744428411</v>
       </c>
       <c r="C11">
-        <v>5.5189315978159681E-2</v>
+        <v>0.05679835090243462</v>
       </c>
       <c r="D11">
-        <v>9.2413432484905633E-2</v>
+        <v>0.09542929240532405</v>
       </c>
       <c r="E11">
-        <v>0.11421672311342281</v>
+        <v>0.1152069007353276</v>
       </c>
       <c r="F11">
-        <v>0.12039094774123769</v>
+        <v>0.1199195314781636</v>
       </c>
       <c r="G11">
-        <v>0.16335506690685961</v>
+        <v>0.1601717363714664</v>
       </c>
       <c r="H11">
-        <v>0.1796502889795375</v>
+        <v>0.1737581688572563</v>
       </c>
       <c r="I11">
-        <v>0.17354662084242431</v>
+        <v>0.1710919361260456</v>
       </c>
       <c r="J11">
-        <v>0.22963808208622349</v>
+        <v>0.2276315334769641</v>
       </c>
       <c r="K11">
-        <v>0.28631023474626971</v>
+        <v>0.2867076168049013</v>
       </c>
       <c r="L11">
-        <v>0.30532151305952743</v>
+        <v>0.3093768295011489</v>
       </c>
       <c r="M11">
-        <v>0.29661543444897082</v>
+        <v>0.3033112286135331</v>
       </c>
       <c r="N11">
-        <v>0.28619145891904357</v>
+        <v>0.2967087114531869</v>
       </c>
       <c r="O11">
-        <v>0.31909102126610073</v>
+        <v>0.3290469499065748</v>
       </c>
       <c r="P11">
-        <v>0.30918318658611232</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>26</v>
+        <v>0.3130030552023214</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B12">
-        <v>2.9661324286891388E-2</v>
+        <v>0.02914609372079713</v>
       </c>
       <c r="C12">
-        <v>5.6496265336447797E-2</v>
+        <v>0.05381344204960448</v>
       </c>
       <c r="D12">
-        <v>9.7736703769851885E-2</v>
+        <v>0.09314978027403631</v>
       </c>
       <c r="E12">
-        <v>0.13594538824357841</v>
+        <v>0.1291843529461419</v>
       </c>
       <c r="F12">
-        <v>0.15857131834033211</v>
+        <v>0.1537144061863323</v>
       </c>
       <c r="G12">
-        <v>0.18211699344292959</v>
+        <v>0.1834298214126971</v>
       </c>
       <c r="H12">
-        <v>0.20496715380200631</v>
+        <v>0.2088262630800779</v>
       </c>
       <c r="I12">
-        <v>0.23901824138414049</v>
+        <v>0.2466428758014111</v>
       </c>
       <c r="J12">
-        <v>0.27089308051558808</v>
+        <v>0.276053156780021</v>
       </c>
       <c r="K12">
-        <v>0.30195673011927221</v>
+        <v>0.3077492972888442</v>
       </c>
       <c r="L12">
-        <v>0.34749677835077603</v>
+        <v>0.3635981130766926</v>
       </c>
       <c r="M12">
-        <v>0.39673577007425481</v>
+        <v>0.4072498875922599</v>
       </c>
       <c r="N12">
-        <v>0.41233629412007028</v>
+        <v>0.4296171078809589</v>
       </c>
       <c r="O12">
-        <v>0.44606503293488381</v>
+        <v>0.4579572076077638</v>
       </c>
       <c r="P12">
-        <v>0.45898545807144892</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>27</v>
+        <v>0.4743661721153724</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+        </is>
       </c>
       <c r="B13">
-        <v>3.170474607602225E-2</v>
+        <v>0.02869480762155396</v>
       </c>
       <c r="C13">
-        <v>6.9197976728660904E-2</v>
+        <v>0.06653544112093801</v>
       </c>
       <c r="D13">
-        <v>0.1059472876886051</v>
+        <v>0.1039501704582317</v>
       </c>
       <c r="E13">
-        <v>0.1247590111767138</v>
+        <v>0.1223762779404374</v>
       </c>
       <c r="F13">
-        <v>0.16422122750767451</v>
+        <v>0.1654446305105143</v>
       </c>
       <c r="G13">
-        <v>0.20819336926048129</v>
+        <v>0.2097123065898014</v>
       </c>
       <c r="H13">
-        <v>0.23351286415742631</v>
+        <v>0.2347815905116317</v>
       </c>
       <c r="I13">
-        <v>0.27876379563217812</v>
+        <v>0.2817724999416855</v>
       </c>
       <c r="J13">
-        <v>0.31381830928317561</v>
+        <v>0.315095471151211</v>
       </c>
       <c r="K13">
-        <v>0.35854654115465828</v>
+        <v>0.3636381592076432</v>
       </c>
       <c r="L13">
-        <v>0.37862887578745469</v>
+        <v>0.3844738515288568</v>
       </c>
       <c r="M13">
-        <v>0.39435305452412878</v>
+        <v>0.4022690369049004</v>
       </c>
       <c r="N13">
-        <v>0.41739190094905759</v>
+        <v>0.4257225005240609</v>
       </c>
       <c r="O13">
-        <v>0.44263262849782548</v>
+        <v>0.4526594064094053</v>
       </c>
       <c r="P13">
-        <v>0.48905609869936478</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>28</v>
+        <v>0.4919759346523158</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B14">
-        <v>3.2805884986460698E-2</v>
+        <v>0.03587539368902198</v>
       </c>
       <c r="C14">
-        <v>5.4827226926406403E-2</v>
+        <v>0.05531721029014502</v>
       </c>
       <c r="D14">
-        <v>8.4014959724313387E-2</v>
+        <v>0.08569099305167072</v>
       </c>
       <c r="E14">
-        <v>7.119241762678985E-2</v>
+        <v>0.07501270860025178</v>
       </c>
       <c r="F14">
-        <v>9.3986169518756824E-2</v>
+        <v>0.09870422180871952</v>
       </c>
       <c r="G14">
-        <v>9.2692717582738782E-2</v>
+        <v>0.09585336368920716</v>
       </c>
       <c r="H14">
-        <v>0.1131105137457727</v>
+        <v>0.1188885332326181</v>
       </c>
       <c r="I14">
-        <v>0.13921409421632239</v>
+        <v>0.1432136667477284</v>
       </c>
       <c r="J14">
-        <v>0.168241085282228</v>
+        <v>0.1712579862358151</v>
       </c>
       <c r="K14">
-        <v>0.184395798484983</v>
+        <v>0.18404964571508</v>
       </c>
       <c r="L14">
-        <v>0.27867584016324709</v>
+        <v>0.2810052418357991</v>
       </c>
       <c r="M14">
-        <v>0.29768163543629628</v>
+        <v>0.300984833206822</v>
       </c>
       <c r="N14">
-        <v>0.28753675684441882</v>
+        <v>0.2880056760425753</v>
       </c>
       <c r="O14">
-        <v>0.28010844307852117</v>
+        <v>0.2859287698507496</v>
       </c>
       <c r="P14">
-        <v>0.2701702388271342</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>29</v>
+        <v>0.2766528470177655</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B15">
-        <v>3.7055999075655773E-2</v>
+        <v>0.03451093854483422</v>
       </c>
       <c r="C15">
-        <v>5.911018418853714E-2</v>
+        <v>0.05501437527350361</v>
       </c>
       <c r="D15">
-        <v>8.6998184689367375E-2</v>
+        <v>0.08434416323030203</v>
       </c>
       <c r="E15">
-        <v>7.5186160397957669E-2</v>
+        <v>0.07349788691893977</v>
       </c>
       <c r="F15">
-        <v>9.8340035355287791E-2</v>
+        <v>0.09712215702374172</v>
       </c>
       <c r="G15">
-        <v>9.5071684829385328E-2</v>
+        <v>0.09296533594996992</v>
       </c>
       <c r="H15">
-        <v>0.1200036904016238</v>
+        <v>0.1168898998289062</v>
       </c>
       <c r="I15">
-        <v>0.14346192317155371</v>
+        <v>0.1391224352776831</v>
       </c>
       <c r="J15">
-        <v>0.16725020840352489</v>
+        <v>0.1653683317816208</v>
       </c>
       <c r="K15">
-        <v>0.18050087985691191</v>
+        <v>0.1761628669824372</v>
       </c>
       <c r="L15">
-        <v>0.26641964931463358</v>
+        <v>0.2616562508666593</v>
       </c>
       <c r="M15">
-        <v>0.29383369884991339</v>
+        <v>0.2900112344125902</v>
       </c>
       <c r="N15">
-        <v>0.28481034095327962</v>
+        <v>0.2831195985919875</v>
       </c>
       <c r="O15">
-        <v>0.27992435687553652</v>
+        <v>0.276195311981123</v>
       </c>
       <c r="P15">
-        <v>0.26825852356630048</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>30</v>
+        <v>0.2649904131681217</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+        </is>
       </c>
       <c r="B16">
-        <v>3.1273774190704602E-2</v>
+        <v>0.0351277124183324</v>
       </c>
       <c r="C16">
-        <v>5.3198421484853653E-2</v>
+        <v>0.05504932194595014</v>
       </c>
       <c r="D16">
-        <v>8.3655899144688961E-2</v>
+        <v>0.08380606774479238</v>
       </c>
       <c r="E16">
-        <v>7.3406488608628417E-2</v>
+        <v>0.07224912025634656</v>
       </c>
       <c r="F16">
-        <v>9.5429457066601442E-2</v>
+        <v>0.09513578923963362</v>
       </c>
       <c r="G16">
-        <v>9.053637021085581E-2</v>
+        <v>0.09119063619605572</v>
       </c>
       <c r="H16">
-        <v>0.1150292263061258</v>
+        <v>0.1153423986496893</v>
       </c>
       <c r="I16">
-        <v>0.13579429965025669</v>
+        <v>0.1372540583565006</v>
       </c>
       <c r="J16">
-        <v>0.16067414887441511</v>
+        <v>0.1637237381038507</v>
       </c>
       <c r="K16">
-        <v>0.17231849702000879</v>
+        <v>0.1729352980500064</v>
       </c>
       <c r="L16">
-        <v>0.25596624211363428</v>
+        <v>0.2566748612296847</v>
       </c>
       <c r="M16">
-        <v>0.27854403163233482</v>
+        <v>0.2811114753220169</v>
       </c>
       <c r="N16">
-        <v>0.26925748105370079</v>
+        <v>0.2723773749574134</v>
       </c>
       <c r="O16">
-        <v>0.26709329569691659</v>
+        <v>0.272800399814811</v>
       </c>
       <c r="P16">
-        <v>0.25662155716756091</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>31</v>
+        <v>0.2631845721700654</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B17">
-        <v>3.4182962961803398E-2</v>
+        <v>0.03534166646945192</v>
       </c>
       <c r="C17">
-        <v>5.6313682296376337E-2</v>
+        <v>0.05697515391664898</v>
       </c>
       <c r="D17">
-        <v>8.3578562669378353E-2</v>
+        <v>0.08942145908372945</v>
       </c>
       <c r="E17">
-        <v>7.2365069076051003E-2</v>
+        <v>0.07707245611164837</v>
       </c>
       <c r="F17">
-        <v>9.5687789869301709E-2</v>
+        <v>0.09934730824698423</v>
       </c>
       <c r="G17">
-        <v>9.1230631409441543E-2</v>
+        <v>0.095289266261811</v>
       </c>
       <c r="H17">
-        <v>0.11340174598757249</v>
+        <v>0.1173805844248862</v>
       </c>
       <c r="I17">
-        <v>0.133752161891149</v>
+        <v>0.1419475766376865</v>
       </c>
       <c r="J17">
-        <v>0.15976180409365709</v>
+        <v>0.1675400611025383</v>
       </c>
       <c r="K17">
-        <v>0.1702070174195576</v>
+        <v>0.1767026443380427</v>
       </c>
       <c r="L17">
-        <v>0.2509823317032942</v>
+        <v>0.2618138023131968</v>
       </c>
       <c r="M17">
-        <v>0.27442878586117508</v>
+        <v>0.2800035903993362</v>
       </c>
       <c r="N17">
-        <v>0.2607686553655828</v>
+        <v>0.2673524902999329</v>
       </c>
       <c r="O17">
-        <v>0.2569325460475218</v>
+        <v>0.2644295502195235</v>
       </c>
       <c r="P17">
-        <v>0.24628498562254589</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>32</v>
+        <v>0.2515505542945174</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B18">
-        <v>3.097309961227768E-2</v>
+        <v>0.02716542399905952</v>
       </c>
       <c r="C18">
-        <v>5.9617912579523653E-2</v>
+        <v>0.05708999692316219</v>
       </c>
       <c r="D18">
-        <v>0.1081564127215817</v>
+        <v>0.1031773195119613</v>
       </c>
       <c r="E18">
-        <v>0.1381901216292202</v>
+        <v>0.1353456164629973</v>
       </c>
       <c r="F18">
-        <v>0.16440548633513419</v>
+        <v>0.1650146929015955</v>
       </c>
       <c r="G18">
-        <v>0.21148252459514141</v>
+        <v>0.2114070418618117</v>
       </c>
       <c r="H18">
-        <v>0.21667769040022769</v>
+        <v>0.2108592326947394</v>
       </c>
       <c r="I18">
-        <v>0.24030590762613779</v>
+        <v>0.2391446164162586</v>
       </c>
       <c r="J18">
-        <v>0.26117470874201909</v>
+        <v>0.2598077587570451</v>
       </c>
       <c r="K18">
-        <v>0.28022703968568241</v>
+        <v>0.2798732378915039</v>
       </c>
       <c r="L18">
-        <v>0.29923261859048927</v>
+        <v>0.300002784343986</v>
       </c>
       <c r="M18">
-        <v>0.33636902939234697</v>
+        <v>0.3354702264048013</v>
       </c>
       <c r="N18">
-        <v>0.3546768881254726</v>
+        <v>0.352554388036844</v>
       </c>
       <c r="O18">
-        <v>0.38521191403923588</v>
+        <v>0.3803521362867375</v>
       </c>
       <c r="P18">
-        <v>0.39059484059045901</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>33</v>
+        <v>0.3856338703287872</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B19">
-        <v>2.8257622060291029E-2</v>
+        <v>0.02634308019358145</v>
       </c>
       <c r="C19">
-        <v>5.596782325997518E-2</v>
+        <v>0.05459334704929286</v>
       </c>
       <c r="D19">
-        <v>8.1203568323561459E-2</v>
+        <v>0.07903470096780629</v>
       </c>
       <c r="E19">
-        <v>0.13300158158091049</v>
+        <v>0.1305412315431416</v>
       </c>
       <c r="F19">
-        <v>0.16137983831161859</v>
+        <v>0.1573799316243517</v>
       </c>
       <c r="G19">
-        <v>0.17954785483274949</v>
+        <v>0.1755326577228296</v>
       </c>
       <c r="H19">
-        <v>0.19482568925606919</v>
+        <v>0.1889272353133274</v>
       </c>
       <c r="I19">
-        <v>0.23193476420883671</v>
+        <v>0.2298286795383506</v>
       </c>
       <c r="J19">
-        <v>0.24773307660402061</v>
+        <v>0.2449532458920306</v>
       </c>
       <c r="K19">
-        <v>0.25188923162884891</v>
+        <v>0.2493039218547063</v>
       </c>
       <c r="L19">
-        <v>0.29471343013522799</v>
+        <v>0.2916811104947786</v>
       </c>
       <c r="M19">
-        <v>0.331370101832272</v>
+        <v>0.3327238031712159</v>
       </c>
       <c r="N19">
-        <v>0.34839369274159088</v>
+        <v>0.3442892769838107</v>
       </c>
       <c r="O19">
-        <v>0.36632733266732082</v>
+        <v>0.364023837392466</v>
       </c>
       <c r="P19">
-        <v>0.36864028503188923</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>34</v>
+        <v>0.3650807547637271</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B20">
-        <v>2.668009558133189E-2</v>
+        <v>0.02798563277763899</v>
       </c>
       <c r="C20">
-        <v>4.8858097121170063E-2</v>
+        <v>0.05243022037874834</v>
       </c>
       <c r="D20">
-        <v>8.5374085573669989E-2</v>
+        <v>0.09326487306060027</v>
       </c>
       <c r="E20">
-        <v>0.14843325113547129</v>
+        <v>0.1529353677412315</v>
       </c>
       <c r="F20">
-        <v>0.1757272004587643</v>
+        <v>0.1797621727344828</v>
       </c>
       <c r="G20">
-        <v>0.17214650304561871</v>
+        <v>0.1752176957654522</v>
       </c>
       <c r="H20">
-        <v>0.17692254986391301</v>
+        <v>0.1865506268338205</v>
       </c>
       <c r="I20">
-        <v>0.2126532037305453</v>
+        <v>0.2207497192212621</v>
       </c>
       <c r="J20">
-        <v>0.21667236129854001</v>
+        <v>0.225012892760482</v>
       </c>
       <c r="K20">
-        <v>0.23277726310508021</v>
+        <v>0.2411125378479516</v>
       </c>
       <c r="L20">
-        <v>0.26594627513318347</v>
+        <v>0.2765854606623551</v>
       </c>
       <c r="M20">
-        <v>0.31210144681278978</v>
+        <v>0.3206012686539764</v>
       </c>
       <c r="N20">
-        <v>0.33147974890217918</v>
+        <v>0.3436608715012681</v>
       </c>
       <c r="O20">
-        <v>0.31898752856792378</v>
+        <v>0.3300540256886996</v>
       </c>
       <c r="P20">
-        <v>0.33446043879921988</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>35</v>
+        <v>0.3452574009193113</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B21">
-        <v>3.9939070161663037E-2</v>
+        <v>0.04345172421075405</v>
       </c>
       <c r="C21">
-        <v>3.9581175112931688E-2</v>
+        <v>0.03963064093790281</v>
       </c>
       <c r="D21">
-        <v>7.1167319995483314E-2</v>
+        <v>0.07050308595075017</v>
       </c>
       <c r="E21">
-        <v>9.1862032778225577E-2</v>
+        <v>0.08770030534906537</v>
       </c>
       <c r="F21">
-        <v>0.1448565897630377</v>
+        <v>0.1456706967234455</v>
       </c>
       <c r="G21">
-        <v>0.1939183178913213</v>
+        <v>0.194765535416684</v>
       </c>
       <c r="H21">
-        <v>0.27798995434779161</v>
+        <v>0.2763285906977116</v>
       </c>
       <c r="I21">
-        <v>0.32178150340247219</v>
+        <v>0.3206878207715273</v>
       </c>
       <c r="J21">
-        <v>0.34588021178096789</v>
+        <v>0.3432542186958948</v>
       </c>
       <c r="K21">
-        <v>0.37946784444360743</v>
+        <v>0.3803644096646063</v>
       </c>
       <c r="L21">
-        <v>0.43072429141710872</v>
+        <v>0.4348467836479759</v>
       </c>
       <c r="M21">
-        <v>0.48171067475047258</v>
+        <v>0.4865545121198229</v>
       </c>
       <c r="N21">
-        <v>0.54476683926382208</v>
+        <v>0.5491989929718858</v>
       </c>
       <c r="O21">
-        <v>0.62539712747386345</v>
+        <v>0.6287682769427272</v>
       </c>
       <c r="P21">
-        <v>0.71286714925463435</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>36</v>
+        <v>0.7170265539002736</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B22">
-        <v>4.0965103877323439E-2</v>
+        <v>0.04269686474637435</v>
       </c>
       <c r="C22">
-        <v>3.9416269418693917E-2</v>
+        <v>0.04124010611571727</v>
       </c>
       <c r="D22">
-        <v>6.9621141227814043E-2</v>
+        <v>0.07189974972789048</v>
       </c>
       <c r="E22">
-        <v>9.198819093919175E-2</v>
+        <v>0.09028483504369544</v>
       </c>
       <c r="F22">
-        <v>0.15087173250902949</v>
+        <v>0.1480675626537903</v>
       </c>
       <c r="G22">
-        <v>0.18316919048106509</v>
+        <v>0.1801104402833137</v>
       </c>
       <c r="H22">
-        <v>0.28162786761958508</v>
+        <v>0.2780234993859931</v>
       </c>
       <c r="I22">
-        <v>0.32904037234454903</v>
+        <v>0.3215182767963077</v>
       </c>
       <c r="J22">
-        <v>0.3587845333324941</v>
+        <v>0.3485655309200437</v>
       </c>
       <c r="K22">
-        <v>0.38440429754457828</v>
+        <v>0.373307600324892</v>
       </c>
       <c r="L22">
-        <v>0.44090761287995311</v>
+        <v>0.4325529921363191</v>
       </c>
       <c r="M22">
-        <v>0.49313119931031468</v>
+        <v>0.4875958363322261</v>
       </c>
       <c r="N22">
-        <v>0.55259848242403264</v>
+        <v>0.5471901497538649</v>
       </c>
       <c r="O22">
-        <v>0.63454000047862935</v>
+        <v>0.6330603893142625</v>
       </c>
       <c r="P22">
-        <v>0.70799997463910169</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>37</v>
+        <v>0.6999827745444558</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B23">
-        <v>3.0397571995501971E-2</v>
+        <v>0.02582907238759691</v>
       </c>
       <c r="C23">
-        <v>9.9992594194912687E-2</v>
+        <v>0.08863871845515131</v>
       </c>
       <c r="D23">
-        <v>0.1046897829260638</v>
+        <v>0.09457248731973789</v>
       </c>
       <c r="E23">
-        <v>9.8196678318504094E-2</v>
+        <v>0.09441008067300827</v>
       </c>
       <c r="F23">
-        <v>0.16806614996039421</v>
+        <v>0.1572553883077732</v>
       </c>
       <c r="G23">
-        <v>0.25835894805303139</v>
+        <v>0.2456270060474</v>
       </c>
       <c r="H23">
-        <v>0.36725056380066229</v>
+        <v>0.3603169417276138</v>
       </c>
       <c r="I23">
-        <v>0.40562710974479238</v>
+        <v>0.400756134688554</v>
       </c>
       <c r="J23">
-        <v>0.47992522673070098</v>
+        <v>0.4712046067760001</v>
       </c>
       <c r="K23">
-        <v>0.54917911997402968</v>
+        <v>0.5354641953601196</v>
       </c>
       <c r="L23">
-        <v>0.62142819692928319</v>
+        <v>0.6023673149116938</v>
       </c>
       <c r="M23">
-        <v>0.65952977873701646</v>
+        <v>0.6437390825217874</v>
       </c>
       <c r="N23">
-        <v>0.72073287324072177</v>
+        <v>0.6996207103595914</v>
       </c>
       <c r="O23">
-        <v>0.78906502375514354</v>
+        <v>0.7696920764147772</v>
       </c>
       <c r="P23">
-        <v>0.86505560396038672</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>38</v>
+        <v>0.8455658134009922</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B24">
-        <v>6.6798312763786255E-2</v>
+        <v>0.02520760487883922</v>
       </c>
       <c r="C24">
-        <v>0.18428319925134509</v>
+        <v>0.04337064195991158</v>
       </c>
       <c r="D24">
-        <v>0.18920825807653041</v>
+        <v>0.0580842185902547</v>
       </c>
       <c r="E24">
-        <v>0.32597110908788191</v>
+        <v>0.06128938453587807</v>
       </c>
       <c r="F24">
-        <v>0.76454089022068561</v>
+        <v>0.09714599711519345</v>
       </c>
       <c r="G24">
-        <v>0.72020956438300121</v>
+        <v>0.1242289793981306</v>
       </c>
       <c r="H24">
-        <v>0.83100402419006136</v>
+        <v>0.138336210114092</v>
       </c>
       <c r="I24">
-        <v>0.93506693453350997</v>
+        <v>0.1960184239262054</v>
       </c>
       <c r="J24">
-        <v>1.051833676755737</v>
+        <v>0.1836417514548523</v>
       </c>
       <c r="K24">
-        <v>1.146153466702593</v>
+        <v>0.1978399186105716</v>
       </c>
       <c r="L24">
-        <v>1.239786530951928</v>
+        <v>0.2564443289452736</v>
       </c>
       <c r="M24">
-        <v>1.311411095654339</v>
+        <v>0.2890782562222076</v>
       </c>
       <c r="N24">
-        <v>1.3477329101665969</v>
+        <v>0.3453644485127993</v>
       </c>
       <c r="O24">
-        <v>1.4237247095890231</v>
+        <v>0.3836093010025138</v>
       </c>
       <c r="P24">
-        <v>1.4600015641488859</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>39</v>
+        <v>0.4400839881748734</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B25">
-        <v>8.6683236440662767E-2</v>
+        <v>0.02364072352628088</v>
       </c>
       <c r="C25">
-        <v>0.18514037076025419</v>
+        <v>0.04009551129678068</v>
       </c>
       <c r="D25">
-        <v>0.25934365329225989</v>
+        <v>0.05616090228892889</v>
       </c>
       <c r="E25">
-        <v>0.43689045627997553</v>
+        <v>0.05640867182383902</v>
       </c>
       <c r="F25">
-        <v>0.58908877839460949</v>
+        <v>0.08757589763836116</v>
       </c>
       <c r="G25">
-        <v>0.78080673708529869</v>
+        <v>0.07979342544667112</v>
       </c>
       <c r="H25">
-        <v>1.0053443974405829</v>
+        <v>0.09337995213076589</v>
       </c>
       <c r="I25">
-        <v>1.135323446148468</v>
+        <v>0.1557347868418913</v>
       </c>
       <c r="J25">
-        <v>1.1898749467764469</v>
+        <v>0.1405299807317625</v>
       </c>
       <c r="K25">
-        <v>1.236281875332391</v>
+        <v>0.150406321649793</v>
       </c>
       <c r="L25">
-        <v>1.384911449944757</v>
+        <v>0.1705449075272835</v>
       </c>
       <c r="M25">
-        <v>1.5286023064766621</v>
+        <v>0.1973239248735515</v>
       </c>
       <c r="N25">
-        <v>1.655983711735179</v>
+        <v>0.2360957836309746</v>
       </c>
       <c r="O25">
-        <v>1.7014702503938419</v>
+        <v>0.2649951127688867</v>
       </c>
       <c r="P25">
-        <v>1.740115060772385</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>40</v>
+        <v>0.3079802786552808</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B26">
-        <v>5.9628753026859549E-2</v>
+        <v>0.02288731418831114</v>
       </c>
       <c r="C26">
-        <v>0.1154776861273364</v>
+        <v>0.04373239935050188</v>
       </c>
       <c r="D26">
-        <v>0.13910615033283719</v>
+        <v>0.07593347284216767</v>
       </c>
       <c r="E26">
-        <v>0.27324726665237942</v>
+        <v>0.06459858816431963</v>
       </c>
       <c r="F26">
-        <v>0.42797089465029431</v>
+        <v>0.09864574965365625</v>
       </c>
       <c r="G26">
-        <v>0.51331347675924233</v>
+        <v>0.09315836471218952</v>
       </c>
       <c r="H26">
-        <v>0.63467501721960196</v>
+        <v>0.120445634040277</v>
       </c>
       <c r="I26">
-        <v>0.61485766771425165</v>
+        <v>0.1517659465396681</v>
       </c>
       <c r="J26">
-        <v>0.59918075040660379</v>
+        <v>0.1876011132638251</v>
       </c>
       <c r="K26">
-        <v>0.60398837093147362</v>
+        <v>0.2083430925829204</v>
       </c>
       <c r="L26">
-        <v>0.78916149662437729</v>
+        <v>0.2343927204671289</v>
       </c>
       <c r="M26">
-        <v>1.0134891754090221</v>
+        <v>0.2536782814813602</v>
       </c>
       <c r="N26">
-        <v>1.001528149196262</v>
+        <v>0.2894711175976804</v>
       </c>
       <c r="O26">
-        <v>1.083863552391475</v>
+        <v>0.3340708495949634</v>
       </c>
       <c r="P26">
-        <v>1.125439844697562</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>41</v>
+        <v>0.3773825713795648</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B27">
-        <v>7.0947176491258077E-2</v>
+        <v>0.02313999811314515</v>
       </c>
       <c r="C27">
-        <v>0.1224220831972465</v>
+        <v>0.04470569157427107</v>
       </c>
       <c r="D27">
-        <v>0.32260044708063079</v>
+        <v>0.07579672461320919</v>
       </c>
       <c r="E27">
-        <v>0.30084860904508842</v>
+        <v>0.06193377917169118</v>
       </c>
       <c r="F27">
-        <v>0.50877453192471256</v>
+        <v>0.09145954173353377</v>
       </c>
       <c r="G27">
-        <v>0.55007550572887332</v>
+        <v>0.09066567752775678</v>
       </c>
       <c r="H27">
-        <v>0.5179943219539177</v>
+        <v>0.1043477641431891</v>
       </c>
       <c r="I27">
-        <v>0.5651019559800865</v>
+        <v>0.1261867305050109</v>
       </c>
       <c r="J27">
-        <v>0.7222263511741227</v>
+        <v>0.1508423678019535</v>
       </c>
       <c r="K27">
-        <v>0.82229581804146079</v>
+        <v>0.1676404185666048</v>
       </c>
       <c r="L27">
-        <v>0.91905283522709258</v>
+        <v>0.1813426498366838</v>
       </c>
       <c r="M27">
-        <v>1.0344182927315171</v>
+        <v>0.1909957525059799</v>
       </c>
       <c r="N27">
-        <v>0.98828676582923092</v>
+        <v>0.2159159065670847</v>
       </c>
       <c r="O27">
-        <v>1.1191702371540131</v>
+        <v>0.2524249021306278</v>
       </c>
       <c r="P27">
-        <v>1.180940013417153</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>42</v>
+        <v>0.253178811327431</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B28">
-        <v>2.5089577855378801E-2</v>
+        <v>0.02549614474681972</v>
       </c>
       <c r="C28">
-        <v>4.3916137786365383E-2</v>
+        <v>0.04540259791793722</v>
       </c>
       <c r="D28">
-        <v>6.144457197386255E-2</v>
+        <v>0.06382889450459961</v>
       </c>
       <c r="E28">
-        <v>6.3048502357768599E-2</v>
+        <v>0.06263721358353458</v>
       </c>
       <c r="F28">
-        <v>0.1013637141551164</v>
+        <v>0.09585565784028649</v>
       </c>
       <c r="G28">
-        <v>0.1242334976231045</v>
+        <v>0.08700520740087381</v>
       </c>
       <c r="H28">
-        <v>0.14511928971709229</v>
+        <v>0.1002140926995647</v>
       </c>
       <c r="I28">
-        <v>0.1955785627029534</v>
+        <v>0.1556630074873068</v>
       </c>
       <c r="J28">
-        <v>0.1844289048333895</v>
+        <v>0.130984046545604</v>
       </c>
       <c r="K28">
-        <v>0.19435441137114881</v>
+        <v>0.131246139025071</v>
       </c>
       <c r="L28">
-        <v>0.25170313323811361</v>
+        <v>0.1324365243045531</v>
       </c>
       <c r="M28">
-        <v>0.28738826720965482</v>
+        <v>0.1473261185336012</v>
       </c>
       <c r="N28">
-        <v>0.34053367301031662</v>
+        <v>0.1691955410931915</v>
       </c>
       <c r="O28">
-        <v>0.37423906429609988</v>
+        <v>0.1910280279368547</v>
       </c>
       <c r="P28">
-        <v>0.42833110533248397</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>43</v>
+        <v>0.2393643477943022</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B29">
-        <v>2.557213430039584E-2</v>
+        <v>0.0244911038061455</v>
       </c>
       <c r="C29">
-        <v>4.5140099914939391E-2</v>
+        <v>0.04360259444424264</v>
       </c>
       <c r="D29">
-        <v>6.1727391396324438E-2</v>
+        <v>0.05935399135445052</v>
       </c>
       <c r="E29">
-        <v>6.0703594714600739E-2</v>
+        <v>0.05680360659220629</v>
       </c>
       <c r="F29">
-        <v>9.1782485839250305E-2</v>
+        <v>0.08426754325600316</v>
       </c>
       <c r="G29">
-        <v>8.4836572703903435E-2</v>
+        <v>0.07852235077832581</v>
       </c>
       <c r="H29">
-        <v>9.7379216613921682E-2</v>
+        <v>0.08396638290441083</v>
       </c>
       <c r="I29">
-        <v>0.16013406238248029</v>
+        <v>0.1361687934094339</v>
       </c>
       <c r="J29">
-        <v>0.1434437130758425</v>
+        <v>0.1181825429698913</v>
       </c>
       <c r="K29">
-        <v>0.15894053142560849</v>
+        <v>0.1194663846951644</v>
       </c>
       <c r="L29">
-        <v>0.17598030634302331</v>
+        <v>0.1191984379110267</v>
       </c>
       <c r="M29">
-        <v>0.20535971289048441</v>
+        <v>0.1350300456072102</v>
       </c>
       <c r="N29">
-        <v>0.24120362290962749</v>
+        <v>0.1565052993151982</v>
       </c>
       <c r="O29">
-        <v>0.27451929552325288</v>
+        <v>0.1780295510488554</v>
       </c>
       <c r="P29">
-        <v>0.31745491550087568</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>44</v>
+        <v>0.2334396665903669</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+        </is>
       </c>
       <c r="B30">
-        <v>2.3848975728812168E-2</v>
+        <v>0.02527124876722542</v>
       </c>
       <c r="C30">
-        <v>4.5770400261148092E-2</v>
+        <v>0.04353310979402447</v>
       </c>
       <c r="D30">
-        <v>8.0565587709346076E-2</v>
+        <v>0.06027812100635233</v>
       </c>
       <c r="E30">
-        <v>6.8793133810551521E-2</v>
+        <v>0.06019784028140107</v>
       </c>
       <c r="F30">
-        <v>0.10121022376216331</v>
+        <v>0.08876265203537148</v>
       </c>
       <c r="G30">
-        <v>9.8087089833930663E-2</v>
+        <v>0.08404312501639055</v>
       </c>
       <c r="H30">
-        <v>0.1240476998053605</v>
+        <v>0.09295643342649451</v>
       </c>
       <c r="I30">
-        <v>0.15964462276849289</v>
+        <v>0.1498235107264411</v>
       </c>
       <c r="J30">
-        <v>0.19278681141880161</v>
+        <v>0.1261167829385882</v>
       </c>
       <c r="K30">
-        <v>0.2128950895530248</v>
+        <v>0.1294066157559226</v>
       </c>
       <c r="L30">
-        <v>0.23960905946625549</v>
+        <v>0.1231867422538043</v>
       </c>
       <c r="M30">
-        <v>0.25935096371651978</v>
+        <v>0.1368942839978097</v>
       </c>
       <c r="N30">
-        <v>0.29777945234814651</v>
+        <v>0.1585668285994519</v>
       </c>
       <c r="O30">
-        <v>0.34335981096139639</v>
+        <v>0.1797219543357995</v>
       </c>
       <c r="P30">
-        <v>0.38950101848326929</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>45</v>
+        <v>0.2351896973650139</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+        </is>
       </c>
       <c r="B31">
-        <v>2.2462716006337868E-2</v>
+        <v>0.02489429176494806</v>
       </c>
       <c r="C31">
-        <v>4.30068945821096E-2</v>
+        <v>0.04291705587651495</v>
       </c>
       <c r="D31">
-        <v>7.5809991886211181E-2</v>
+        <v>0.0611393500073969</v>
       </c>
       <c r="E31">
-        <v>6.3882856623741269E-2</v>
+        <v>0.05952096628932091</v>
       </c>
       <c r="F31">
-        <v>9.4923567741025505E-2</v>
+        <v>0.08738504408730152</v>
       </c>
       <c r="G31">
-        <v>8.7801225867549904E-2</v>
+        <v>0.08155013384898935</v>
       </c>
       <c r="H31">
-        <v>0.10397452827060349</v>
+        <v>0.08915845698758462</v>
       </c>
       <c r="I31">
-        <v>0.12562838443853319</v>
+        <v>0.1447674679708304</v>
       </c>
       <c r="J31">
-        <v>0.15164250675461971</v>
+        <v>0.1234864656047783</v>
       </c>
       <c r="K31">
-        <v>0.1713053824921951</v>
+        <v>0.1302266581740626</v>
       </c>
       <c r="L31">
-        <v>0.18269598606998541</v>
+        <v>0.1211668713032732</v>
       </c>
       <c r="M31">
-        <v>0.1920659688399641</v>
+        <v>0.1360507906704093</v>
       </c>
       <c r="N31">
-        <v>0.21643519542252829</v>
+        <v>0.1583852384964946</v>
       </c>
       <c r="O31">
-        <v>0.25793410054427868</v>
+        <v>0.1712837673827533</v>
       </c>
       <c r="P31">
-        <v>0.25661879314238162</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>46</v>
+        <v>0.2229429332248543</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B32">
-        <v>2.4723769785070741E-2</v>
+        <v>0.02405821285096332</v>
       </c>
       <c r="C32">
-        <v>4.3957323922983238E-2</v>
+        <v>0.04401634023103806</v>
       </c>
       <c r="D32">
-        <v>6.1947228248644959E-2</v>
+        <v>0.06183944395685137</v>
       </c>
       <c r="E32">
-        <v>6.0385788693393512E-2</v>
+        <v>0.06092988172126979</v>
       </c>
       <c r="F32">
-        <v>9.2090638588247731E-2</v>
+        <v>0.09365564850735564</v>
       </c>
       <c r="G32">
-        <v>8.5645763039838063E-2</v>
+        <v>0.08548209239300475</v>
       </c>
       <c r="H32">
-        <v>9.3269791841922078E-2</v>
+        <v>0.09730915573431542</v>
       </c>
       <c r="I32">
-        <v>0.14921764244128291</v>
+        <v>0.1493033089718551</v>
       </c>
       <c r="J32">
-        <v>0.12964232790074959</v>
+        <v>0.1297648136913101</v>
       </c>
       <c r="K32">
-        <v>0.13086278420122049</v>
+        <v>0.1342473144203536</v>
       </c>
       <c r="L32">
-        <v>0.13304610795988281</v>
+        <v>0.1423065075878095</v>
       </c>
       <c r="M32">
-        <v>0.14747916404728451</v>
+        <v>0.1600196138666152</v>
       </c>
       <c r="N32">
-        <v>0.17080642454989939</v>
+        <v>0.1851289231304631</v>
       </c>
       <c r="O32">
-        <v>0.1931355189071832</v>
+        <v>0.2039885844441082</v>
       </c>
       <c r="P32">
-        <v>0.24638626378808451</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>47</v>
+        <v>0.2532280224303115</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+        </is>
       </c>
       <c r="B33">
-        <v>2.4160351851025719E-2</v>
+        <v>0.02426138064052108</v>
       </c>
       <c r="C33">
-        <v>4.3462861429619297E-2</v>
+        <v>0.04400141193571205</v>
       </c>
       <c r="D33">
-        <v>6.0366829026244677E-2</v>
+        <v>0.06202512941987481</v>
       </c>
       <c r="E33">
-        <v>5.9813314666671058E-2</v>
+        <v>0.06044709278000071</v>
       </c>
       <c r="F33">
-        <v>9.0127169882396552E-2</v>
+        <v>0.09062925467574212</v>
       </c>
       <c r="G33">
-        <v>8.4758375061715463E-2</v>
+        <v>0.0844541626577382</v>
       </c>
       <c r="H33">
-        <v>9.236584938682646E-2</v>
+        <v>0.09504405281446304</v>
       </c>
       <c r="I33">
-        <v>0.14777249211835791</v>
+        <v>0.1460620335001227</v>
       </c>
       <c r="J33">
-        <v>0.1215913034174968</v>
+        <v>0.1269930070804374</v>
       </c>
       <c r="K33">
-        <v>0.12671148779433969</v>
+        <v>0.1350033115178284</v>
       </c>
       <c r="L33">
-        <v>0.1246600199894117</v>
+        <v>0.1378800778932727</v>
       </c>
       <c r="M33">
-        <v>0.14096108871966281</v>
+        <v>0.1577425912349429</v>
       </c>
       <c r="N33">
-        <v>0.16230456897203679</v>
+        <v>0.1803167907735369</v>
       </c>
       <c r="O33">
-        <v>0.18599558812189429</v>
+        <v>0.2053801490357965</v>
       </c>
       <c r="P33">
-        <v>0.2380015867308555</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>48</v>
+        <v>0.2578835338085539</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+        </is>
       </c>
       <c r="B34">
-        <v>2.4562519756207931E-2</v>
+        <v>0.02595814934499174</v>
       </c>
       <c r="C34">
-        <v>4.3745961466054473E-2</v>
+        <v>0.04441650573266853</v>
       </c>
       <c r="D34">
-        <v>6.075021552433868E-2</v>
+        <v>0.06171703904237791</v>
       </c>
       <c r="E34">
-        <v>5.9978138524392821E-2</v>
+        <v>0.05980946539091103</v>
       </c>
       <c r="F34">
-        <v>9.0143571931937561E-2</v>
+        <v>0.08975759051130239</v>
       </c>
       <c r="G34">
-        <v>8.1553319455166307E-2</v>
+        <v>0.08320418118266171</v>
       </c>
       <c r="H34">
-        <v>9.0399210085953308E-2</v>
+        <v>0.09189741100663251</v>
       </c>
       <c r="I34">
-        <v>0.14566824546289101</v>
+        <v>0.1407533213113548</v>
       </c>
       <c r="J34">
-        <v>0.12559009622334361</v>
+        <v>0.1232802404126729</v>
       </c>
       <c r="K34">
-        <v>0.1247381261630007</v>
+        <v>0.1295269068546554</v>
       </c>
       <c r="L34">
-        <v>0.1201014150438299</v>
+        <v>0.1339125541074727</v>
       </c>
       <c r="M34">
-        <v>0.1354623558632537</v>
+        <v>0.1478920445834784</v>
       </c>
       <c r="N34">
-        <v>0.15929412911788751</v>
+        <v>0.1713079760047426</v>
       </c>
       <c r="O34">
-        <v>0.17673281569641711</v>
+        <v>0.1920946173415038</v>
       </c>
       <c r="P34">
-        <v>0.23012561104156831</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>49</v>
+        <v>0.2500387417124901</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B35">
-        <v>2.4428611326919539E-2</v>
+        <v>0.02483015894269425</v>
       </c>
       <c r="C35">
-        <v>4.3675365211720329E-2</v>
+        <v>0.04344310532274609</v>
       </c>
       <c r="D35">
-        <v>6.1603478971335779E-2</v>
+        <v>0.06062227161057809</v>
       </c>
       <c r="E35">
-        <v>5.9590480955062593E-2</v>
+        <v>0.06014437886789326</v>
       </c>
       <c r="F35">
-        <v>8.7944437464977487E-2</v>
+        <v>0.09008358712170672</v>
       </c>
       <c r="G35">
-        <v>8.1307021278267499E-2</v>
+        <v>0.08252412855810809</v>
       </c>
       <c r="H35">
-        <v>8.9809966277786701E-2</v>
+        <v>0.09095123054821497</v>
       </c>
       <c r="I35">
-        <v>0.14558733076153019</v>
+        <v>0.1415871942023978</v>
       </c>
       <c r="J35">
-        <v>0.1232481534921297</v>
+        <v>0.1239463707242203</v>
       </c>
       <c r="K35">
-        <v>0.1296282325764602</v>
+        <v>0.1286135125359177</v>
       </c>
       <c r="L35">
-        <v>0.120836308512142</v>
+        <v>0.1327289513741623</v>
       </c>
       <c r="M35">
-        <v>0.1346208028090555</v>
+        <v>0.1463994702265876</v>
       </c>
       <c r="N35">
-        <v>0.15538235547845461</v>
+        <v>0.1676264392014841</v>
       </c>
       <c r="O35">
-        <v>0.17317698498889</v>
+        <v>0.1877994263490738</v>
       </c>
       <c r="P35">
-        <v>0.22495737650526129</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>50</v>
+        <v>0.2411494328662095</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B36">
-        <v>2.5062006559130271E-2</v>
+        <v>0.02553672748989522</v>
       </c>
       <c r="C36">
-        <v>4.2916740027126088E-2</v>
+        <v>0.04481135730785912</v>
       </c>
       <c r="D36">
-        <v>6.1013945618519923E-2</v>
+        <v>0.0618058116864838</v>
       </c>
       <c r="E36">
-        <v>6.0146968288713687E-2</v>
+        <v>0.06088335084325236</v>
       </c>
       <c r="F36">
-        <v>8.8123298108919834E-2</v>
+        <v>0.08856641852741187</v>
       </c>
       <c r="G36">
-        <v>8.191790864295434E-2</v>
+        <v>0.08275346573850306</v>
       </c>
       <c r="H36">
-        <v>9.1391577679855618E-2</v>
+        <v>0.09176098609913863</v>
       </c>
       <c r="I36">
-        <v>0.14112833252511059</v>
+        <v>0.1457638507743987</v>
       </c>
       <c r="J36">
-        <v>0.1222702788384824</v>
+        <v>0.1242990499470922</v>
       </c>
       <c r="K36">
-        <v>0.12868007384983821</v>
+        <v>0.132345047507578</v>
       </c>
       <c r="L36">
-        <v>0.13797536971058519</v>
+        <v>0.1241436408284494</v>
       </c>
       <c r="M36">
-        <v>0.15517176698472809</v>
+        <v>0.1382786264716538</v>
       </c>
       <c r="N36">
-        <v>0.18314423980216099</v>
+        <v>0.1575309152842922</v>
       </c>
       <c r="O36">
-        <v>0.20145509892535951</v>
+        <v>0.1673907905953755</v>
       </c>
       <c r="P36">
-        <v>0.2487927252278764</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>51</v>
+        <v>0.2253061358959476</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B37">
-        <v>2.603196982989919E-2</v>
+        <v>0.02515782318774862</v>
       </c>
       <c r="C37">
-        <v>4.4970418171162208E-2</v>
+        <v>0.1269201447649507</v>
       </c>
       <c r="D37">
-        <v>6.072294965295344E-2</v>
+        <v>0.08012670541043099</v>
       </c>
       <c r="E37">
-        <v>5.9367599933660482E-2</v>
+        <v>0.09057134587553684</v>
       </c>
       <c r="F37">
-        <v>8.9579637428362058E-2</v>
+        <v>0.1361220311843149</v>
       </c>
       <c r="G37">
-        <v>8.2818941730974371E-2</v>
+        <v>0.2272681785286651</v>
       </c>
       <c r="H37">
-        <v>9.0287391705176745E-2</v>
+        <v>0.2489245888233611</v>
       </c>
       <c r="I37">
-        <v>0.14510825725645229</v>
+        <v>0.2817394233023909</v>
       </c>
       <c r="J37">
-        <v>0.1245962082251295</v>
+        <v>0.3114558181630881</v>
       </c>
       <c r="K37">
-        <v>0.13077819452979661</v>
+        <v>0.3219249620603957</v>
       </c>
       <c r="L37">
-        <v>0.13702109075040839</v>
+        <v>0.3605379582786322</v>
       </c>
       <c r="M37">
-        <v>0.1554104600533377</v>
+        <v>0.3736799560532534</v>
       </c>
       <c r="N37">
-        <v>0.18216397736493131</v>
+        <v>0.4006575129444598</v>
       </c>
       <c r="O37">
-        <v>0.20508714524753929</v>
+        <v>0.4239583315822448</v>
       </c>
       <c r="P37">
-        <v>0.25400716406064061</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>52</v>
+        <v>0.4390403821144105</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+        </is>
       </c>
       <c r="B38">
-        <v>2.459263824912605E-2</v>
+        <v>0.02524938955697642</v>
       </c>
       <c r="C38">
-        <v>4.2777044811612368E-2</v>
+        <v>0.1159964529322793</v>
       </c>
       <c r="D38">
-        <v>6.0740001131238557E-2</v>
+        <v>0.06254125969142832</v>
       </c>
       <c r="E38">
-        <v>5.9465628946525302E-2</v>
+        <v>0.07495666112378818</v>
       </c>
       <c r="F38">
-        <v>9.0740913881234175E-2</v>
+        <v>0.1217390179884419</v>
       </c>
       <c r="G38">
-        <v>8.3668683220170736E-2</v>
+        <v>0.1974759461146453</v>
       </c>
       <c r="H38">
-        <v>9.2825043142131691E-2</v>
+        <v>0.2029950007150344</v>
       </c>
       <c r="I38">
-        <v>0.1423725602251725</v>
+        <v>0.2170478633686548</v>
       </c>
       <c r="J38">
-        <v>0.12355855319050291</v>
+        <v>0.219287677230977</v>
       </c>
       <c r="K38">
-        <v>0.12846751938449791</v>
+        <v>0.2147154894156721</v>
       </c>
       <c r="L38">
-        <v>0.13433906719342811</v>
+        <v>0.228243327022714</v>
       </c>
       <c r="M38">
-        <v>0.14802910296179081</v>
+        <v>0.2470727245569495</v>
       </c>
       <c r="N38">
-        <v>0.17150860971788681</v>
+        <v>0.25633262774086</v>
       </c>
       <c r="O38">
-        <v>0.19103679194833451</v>
+        <v>0.28618182310013</v>
       </c>
       <c r="P38">
-        <v>0.25329738002399499</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>53</v>
+        <v>0.3335909622061869</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B39">
-        <v>2.3985964471841651E-2</v>
+        <v>0.02414147282829449</v>
       </c>
       <c r="C39">
-        <v>4.3309932660338002E-2</v>
+        <v>0.1084894201294527</v>
       </c>
       <c r="D39">
-        <v>5.9193098122343628E-2</v>
+        <v>0.05732913103499648</v>
       </c>
       <c r="E39">
-        <v>5.8101167509179263E-2</v>
+        <v>0.07102116662250091</v>
       </c>
       <c r="F39">
-        <v>8.8290601770394384E-2</v>
+        <v>0.1265541448776214</v>
       </c>
       <c r="G39">
-        <v>8.0301260148129439E-2</v>
+        <v>0.179100398785133</v>
       </c>
       <c r="H39">
-        <v>9.2277603079697124E-2</v>
+        <v>0.1715597874735505</v>
       </c>
       <c r="I39">
-        <v>0.144666228384011</v>
+        <v>0.1908157535622973</v>
       </c>
       <c r="J39">
-        <v>0.1228316707019949</v>
+        <v>0.1929810920260993</v>
       </c>
       <c r="K39">
-        <v>0.12688543017727719</v>
+        <v>0.1942183555059604</v>
       </c>
       <c r="L39">
-        <v>0.13265268008561429</v>
+        <v>0.2170973462542523</v>
       </c>
       <c r="M39">
-        <v>0.1480550085757307</v>
+        <v>0.2359561166782166</v>
       </c>
       <c r="N39">
-        <v>0.16718999282932259</v>
+        <v>0.2419584078034192</v>
       </c>
       <c r="O39">
-        <v>0.1909276178765513</v>
+        <v>0.2549626987919298</v>
       </c>
       <c r="P39">
-        <v>0.24830837509371301</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>54</v>
+        <v>0.3009361625212156</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+        </is>
       </c>
       <c r="B40">
-        <v>2.367106427108789E-2</v>
+        <v>0.0325956632207326</v>
       </c>
       <c r="C40">
-        <v>4.3357192647390352E-2</v>
+        <v>0.09689168039439355</v>
       </c>
       <c r="D40">
-        <v>6.2294623284278712E-2</v>
+        <v>0.1160853761587609</v>
       </c>
       <c r="E40">
-        <v>6.0894923275267472E-2</v>
+        <v>0.07402713696695973</v>
       </c>
       <c r="F40">
-        <v>9.0973268377082972E-2</v>
+        <v>0.1294511650719864</v>
       </c>
       <c r="G40">
-        <v>8.5037899088389213E-2</v>
+        <v>0.1634526907588006</v>
       </c>
       <c r="H40">
-        <v>9.4043545818516039E-2</v>
+        <v>0.2004389790979527</v>
       </c>
       <c r="I40">
-        <v>0.1503291154307986</v>
+        <v>0.2236085258608619</v>
       </c>
       <c r="J40">
-        <v>0.12656988331146879</v>
+        <v>0.2514227742121161</v>
       </c>
       <c r="K40">
-        <v>0.13321900533052181</v>
+        <v>0.300149005327681</v>
       </c>
       <c r="L40">
-        <v>0.12329617185782191</v>
+        <v>0.3512710714185012</v>
       </c>
       <c r="M40">
-        <v>0.13836937382391809</v>
+        <v>0.3924549050657671</v>
       </c>
       <c r="N40">
-        <v>0.15774317941723229</v>
+        <v>0.4348676993765227</v>
       </c>
       <c r="O40">
-        <v>0.16920336584645931</v>
+        <v>0.4710218421823752</v>
       </c>
       <c r="P40">
-        <v>0.22469639272824249</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>55</v>
+        <v>0.5319256355636595</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(1,3,5)_</t>
+        </is>
       </c>
       <c r="B41">
-        <v>2.5390968813600919E-2</v>
+        <v>0.03911208951006995</v>
       </c>
       <c r="C41">
-        <v>0.1194115580096166</v>
+        <v>0.0600814009862215</v>
       </c>
       <c r="D41">
-        <v>7.5124591080072634E-2</v>
+        <v>0.1294245906949427</v>
       </c>
       <c r="E41">
-        <v>8.8086035526678708E-2</v>
+        <v>0.2024254635943428</v>
       </c>
       <c r="F41">
-        <v>0.13393981452795509</v>
+        <v>0.3021121100028604</v>
       </c>
       <c r="G41">
-        <v>0.22567163669438459</v>
+        <v>0.3669815690638776</v>
       </c>
       <c r="H41">
-        <v>0.2468855759544584</v>
+        <v>0.3760932382141777</v>
       </c>
       <c r="I41">
-        <v>0.28188786768343688</v>
+        <v>0.3848763831394686</v>
       </c>
       <c r="J41">
-        <v>0.31317076648740028</v>
+        <v>0.4135469531487526</v>
       </c>
       <c r="K41">
-        <v>0.3239335147847372</v>
+        <v>0.5195376927856628</v>
       </c>
       <c r="L41">
-        <v>0.36261442965624979</v>
+        <v>0.5904137166068192</v>
       </c>
       <c r="M41">
-        <v>0.37449475585635089</v>
+        <v>0.6342872486949386</v>
       </c>
       <c r="N41">
-        <v>0.39874147922088948</v>
+        <v>0.7120285519721135</v>
       </c>
       <c r="O41">
-        <v>0.4234474486974763</v>
+        <v>0.7626384906325988</v>
       </c>
       <c r="P41">
-        <v>0.44045552637795032</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>56</v>
+        <v>0.7490552491448548</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B42">
-        <v>2.474988438987091E-2</v>
+        <v>0.05028833097319457</v>
       </c>
       <c r="C42">
-        <v>0.112677674330515</v>
+        <v>0.04958541380583037</v>
       </c>
       <c r="D42">
-        <v>6.1268325752683588E-2</v>
+        <v>0.1125177861354478</v>
       </c>
       <c r="E42">
-        <v>7.5940424419506658E-2</v>
+        <v>0.1649927745977939</v>
       </c>
       <c r="F42">
-        <v>0.1219945364638949</v>
+        <v>0.2583627938361128</v>
       </c>
       <c r="G42">
-        <v>0.19429460915187871</v>
+        <v>0.2523320297513386</v>
       </c>
       <c r="H42">
-        <v>0.20252517751782381</v>
+        <v>0.2916287812319721</v>
       </c>
       <c r="I42">
-        <v>0.22026339047817339</v>
+        <v>0.3611400847863658</v>
       </c>
       <c r="J42">
-        <v>0.22103584019133329</v>
+        <v>0.4543033432074002</v>
       </c>
       <c r="K42">
-        <v>0.21598549106752399</v>
+        <v>0.5545595960702747</v>
       </c>
       <c r="L42">
-        <v>0.2311703268124469</v>
+        <v>0.5946491974959374</v>
       </c>
       <c r="M42">
-        <v>0.25108251223559491</v>
+        <v>0.6416702384527113</v>
       </c>
       <c r="N42">
-        <v>0.2590784989240501</v>
+        <v>0.6765043764821863</v>
       </c>
       <c r="O42">
-        <v>0.2853638637691932</v>
+        <v>0.7002320713777599</v>
       </c>
       <c r="P42">
-        <v>0.33198248813713638</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>57</v>
+        <v>0.7073414785800279</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+        </is>
       </c>
       <c r="B43">
-        <v>2.5963540494163939E-2</v>
+        <v>0.03091460870690554</v>
       </c>
       <c r="C43">
-        <v>0.1143007045334147</v>
+        <v>0.0908348543064893</v>
       </c>
       <c r="D43">
-        <v>6.1185332922271463E-2</v>
+        <v>0.1350761452433041</v>
       </c>
       <c r="E43">
-        <v>7.5916714441661037E-2</v>
+        <v>0.1995284119300154</v>
       </c>
       <c r="F43">
-        <v>0.12935643841403119</v>
+        <v>0.342922189694562</v>
       </c>
       <c r="G43">
-        <v>0.1874834826425551</v>
+        <v>0.3433451653043718</v>
       </c>
       <c r="H43">
-        <v>0.18267383573738841</v>
+        <v>0.3335610063644278</v>
       </c>
       <c r="I43">
-        <v>0.20175018280778181</v>
+        <v>0.3505130045545088</v>
       </c>
       <c r="J43">
-        <v>0.2038519814411193</v>
+        <v>0.4453470510902236</v>
       </c>
       <c r="K43">
-        <v>0.20419024742942729</v>
+        <v>0.4617874412115183</v>
       </c>
       <c r="L43">
-        <v>0.22140725438853201</v>
+        <v>0.5216394269749918</v>
       </c>
       <c r="M43">
-        <v>0.24390849623401609</v>
+        <v>0.5518392326288292</v>
       </c>
       <c r="N43">
-        <v>0.24738982267244769</v>
+        <v>0.55360228825728</v>
       </c>
       <c r="O43">
-        <v>0.26162000857662582</v>
+        <v>0.5645908477109998</v>
       </c>
       <c r="P43">
-        <v>0.30502710143214617</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>58</v>
-      </c>
-      <c r="B44">
-        <v>3.0988070394335491E-2</v>
-      </c>
-      <c r="C44">
-        <v>9.0525787226068966E-2</v>
-      </c>
-      <c r="D44">
-        <v>0.11134330849386539</v>
-      </c>
-      <c r="E44">
-        <v>7.0284598014564548E-2</v>
-      </c>
-      <c r="F44">
-        <v>0.1261405110554541</v>
-      </c>
-      <c r="G44">
-        <v>0.15581267938134311</v>
-      </c>
-      <c r="H44">
-        <v>0.1982106752992836</v>
-      </c>
-      <c r="I44">
-        <v>0.2184809520107476</v>
-      </c>
-      <c r="J44">
-        <v>0.24728910426391909</v>
-      </c>
-      <c r="K44">
-        <v>0.29849189631538731</v>
-      </c>
-      <c r="L44">
-        <v>0.3508380105691925</v>
-      </c>
-      <c r="M44">
-        <v>0.39104744037691852</v>
-      </c>
-      <c r="N44">
-        <v>0.42940635013282658</v>
-      </c>
-      <c r="O44">
-        <v>0.46641038420682063</v>
-      </c>
-      <c r="P44">
-        <v>0.52814793276832761</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>59</v>
-      </c>
-      <c r="B45">
-        <v>4.0046141662883339E-2</v>
-      </c>
-      <c r="C45">
-        <v>6.4265165893398479E-2</v>
-      </c>
-      <c r="D45">
-        <v>0.13246336208018719</v>
-      </c>
-      <c r="E45">
-        <v>0.2018495102669324</v>
-      </c>
-      <c r="F45">
-        <v>0.2956611313275701</v>
-      </c>
-      <c r="G45">
-        <v>0.35444510564309872</v>
-      </c>
-      <c r="H45">
-        <v>0.3628997647706631</v>
-      </c>
-      <c r="I45">
-        <v>0.37897476082936787</v>
-      </c>
-      <c r="J45">
-        <v>0.40936707991830129</v>
-      </c>
-      <c r="K45">
-        <v>0.51154300743051184</v>
-      </c>
-      <c r="L45">
-        <v>0.58560801273952734</v>
-      </c>
-      <c r="M45">
-        <v>0.63081197820879942</v>
-      </c>
-      <c r="N45">
-        <v>0.70585086948846465</v>
-      </c>
-      <c r="O45">
-        <v>0.74908140116666067</v>
-      </c>
-      <c r="P45">
-        <v>0.73692877775671062</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>60</v>
-      </c>
-      <c r="B46">
-        <v>4.6777482586753523E-2</v>
-      </c>
-      <c r="C46">
-        <v>4.6260938638123313E-2</v>
-      </c>
-      <c r="D46">
-        <v>0.1042264529030448</v>
-      </c>
-      <c r="E46">
-        <v>0.16201054752210339</v>
-      </c>
-      <c r="F46">
-        <v>0.24954866208469129</v>
-      </c>
-      <c r="G46">
-        <v>0.24702660583109129</v>
-      </c>
-      <c r="H46">
-        <v>0.28254282059237751</v>
-      </c>
-      <c r="I46">
-        <v>0.34851079798926371</v>
-      </c>
-      <c r="J46">
-        <v>0.44265018017266389</v>
-      </c>
-      <c r="K46">
-        <v>0.54977677825621263</v>
-      </c>
-      <c r="L46">
-        <v>0.5940487585320855</v>
-      </c>
-      <c r="M46">
-        <v>0.6370679258050439</v>
-      </c>
-      <c r="N46">
-        <v>0.67255025977287808</v>
-      </c>
-      <c r="O46">
-        <v>0.69587444675024379</v>
-      </c>
-      <c r="P46">
-        <v>0.69936524815328538</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>61</v>
-      </c>
-      <c r="B47">
-        <v>3.341212425483675E-2</v>
-      </c>
-      <c r="C47">
-        <v>9.5965316816099322E-2</v>
-      </c>
-      <c r="D47">
-        <v>0.14154945853889761</v>
-      </c>
-      <c r="E47">
-        <v>0.20504528536010111</v>
-      </c>
-      <c r="F47">
-        <v>0.34988525713856677</v>
-      </c>
-      <c r="G47">
-        <v>0.34813655380133768</v>
-      </c>
-      <c r="H47">
-        <v>0.3390595290928769</v>
-      </c>
-      <c r="I47">
-        <v>0.35526770948806669</v>
-      </c>
-      <c r="J47">
-        <v>0.45015267980469098</v>
-      </c>
-      <c r="K47">
-        <v>0.46888383434621778</v>
-      </c>
-      <c r="L47">
-        <v>0.52778122368904912</v>
-      </c>
-      <c r="M47">
-        <v>0.56191762255768096</v>
-      </c>
-      <c r="N47">
-        <v>0.56277863304306219</v>
-      </c>
-      <c r="O47">
-        <v>0.57286187657253107</v>
-      </c>
-      <c r="P47">
-        <v>0.58450260341115023</v>
+        <v>0.5745349825537128</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:P47">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
-      <formula>0.2</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <formula>0.2</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>